--- a/research/traditional_assets/database/data/mexico/mexico_steel.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_steel.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1132565372525995</v>
+        <v>0.1129482676408417</v>
       </c>
       <c r="C2">
-        <v>3394.272380387607</v>
+        <v>3368.911872992307</v>
       </c>
       <c r="D2">
-        <v>1869.472380387607</v>
+        <v>1878.054902992307</v>
       </c>
       <c r="E2">
-        <v>-0.303</v>
+        <v>33.64003</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>33.94303</v>
       </c>
       <c r="G2">
         <v>1524.8</v>
@@ -1579,28 +1579,28 @@
         <v>325.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.707334409</v>
       </c>
       <c r="N2">
-        <v>325.8</v>
+        <v>324.092665591</v>
       </c>
       <c r="O2">
-        <v>97.73999999999999</v>
+        <v>97.2277996773</v>
       </c>
       <c r="P2">
-        <v>228.06</v>
+        <v>226.8648659137</v>
       </c>
       <c r="Q2">
-        <v>284.86</v>
+        <v>283.6648659137001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1132565372525995</v>
+        <v>0.1137335026675169</v>
       </c>
       <c r="T2">
-        <v>0.9815748103161358</v>
+        <v>0.988515238267866</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>190.8237766910724</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1129482676408417</v>
+        <v>0.1126399980290839</v>
       </c>
       <c r="C3">
-        <v>3368.911872992307</v>
+        <v>3343.630531694832</v>
       </c>
       <c r="D3">
-        <v>1878.054902992307</v>
+        <v>1886.716591694832</v>
       </c>
       <c r="E3">
-        <v>33.64003</v>
+        <v>67.58306</v>
       </c>
       <c r="F3">
-        <v>33.94303</v>
+        <v>67.88606</v>
       </c>
       <c r="G3">
         <v>1524.8</v>
@@ -1661,28 +1661,28 @@
         <v>325.8</v>
       </c>
       <c r="M3">
-        <v>1.707334409</v>
+        <v>3.414668818</v>
       </c>
       <c r="N3">
-        <v>324.092665591</v>
+        <v>322.385331182</v>
       </c>
       <c r="O3">
-        <v>97.2277996773</v>
+        <v>96.7155993546</v>
       </c>
       <c r="P3">
-        <v>226.8648659137</v>
+        <v>225.6697318274</v>
       </c>
       <c r="Q3">
-        <v>283.6648659137001</v>
+        <v>282.4697318274</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1137335026675169</v>
+        <v>0.1142202020704938</v>
       </c>
       <c r="T3">
-        <v>0.988515238267866</v>
+        <v>0.9955973076063662</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>190.8237766910724</v>
+        <v>95.41188834553618</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1126399980290839</v>
+        <v>0.1123317284173261</v>
       </c>
       <c r="C4">
-        <v>3343.630531694832</v>
+        <v>3318.429456925132</v>
       </c>
       <c r="D4">
-        <v>1886.716591694832</v>
+        <v>1895.458546925133</v>
       </c>
       <c r="E4">
-        <v>67.58306</v>
+        <v>101.52609</v>
       </c>
       <c r="F4">
-        <v>67.88606</v>
+        <v>101.82909</v>
       </c>
       <c r="G4">
         <v>1524.8</v>
@@ -1743,28 +1743,28 @@
         <v>325.8</v>
       </c>
       <c r="M4">
-        <v>3.414668818</v>
+        <v>5.122003227</v>
       </c>
       <c r="N4">
-        <v>322.385331182</v>
+        <v>320.677996773</v>
       </c>
       <c r="O4">
-        <v>96.7155993546</v>
+        <v>96.20339903190001</v>
       </c>
       <c r="P4">
-        <v>225.6697318274</v>
+        <v>224.4745977411</v>
       </c>
       <c r="Q4">
-        <v>282.4697318274</v>
+        <v>281.2745977411</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1142202020704938</v>
+        <v>0.1147169365127074</v>
       </c>
       <c r="T4">
-        <v>0.9955973076063662</v>
+        <v>1.002825398993083</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>95.41188834553618</v>
+        <v>63.60792556369079</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1123317284173261</v>
+        <v>0.1120234588055684</v>
       </c>
       <c r="C5">
-        <v>3318.429456925132</v>
+        <v>3293.309769603127</v>
       </c>
       <c r="D5">
-        <v>1895.458546925133</v>
+        <v>1904.281889603127</v>
       </c>
       <c r="E5">
-        <v>101.52609</v>
+        <v>135.46912</v>
       </c>
       <c r="F5">
-        <v>101.82909</v>
+        <v>135.77212</v>
       </c>
       <c r="G5">
         <v>1524.8</v>
@@ -1825,28 +1825,28 @@
         <v>325.8</v>
       </c>
       <c r="M5">
-        <v>5.122003227</v>
+        <v>6.829337636</v>
       </c>
       <c r="N5">
-        <v>320.677996773</v>
+        <v>318.970662364</v>
       </c>
       <c r="O5">
-        <v>96.20339903190001</v>
+        <v>95.69119870920001</v>
       </c>
       <c r="P5">
-        <v>224.4745977411</v>
+        <v>223.2794636548</v>
       </c>
       <c r="Q5">
-        <v>281.2745977411</v>
+        <v>280.0794636548</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1147169365127074</v>
+        <v>0.1152240195891337</v>
       </c>
       <c r="T5">
-        <v>1.002825398993083</v>
+        <v>1.010204075617023</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.60792556369079</v>
+        <v>47.70594417276809</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1120234588055684</v>
+        <v>0.1117151891938105</v>
       </c>
       <c r="C6">
-        <v>3293.309769603127</v>
+        <v>3268.272611617836</v>
       </c>
       <c r="D6">
-        <v>1904.281889603127</v>
+        <v>1913.187761617836</v>
       </c>
       <c r="E6">
-        <v>135.46912</v>
+        <v>169.41215</v>
       </c>
       <c r="F6">
-        <v>135.77212</v>
+        <v>169.71515</v>
       </c>
       <c r="G6">
         <v>1524.8</v>
@@ -1907,28 +1907,28 @@
         <v>325.8</v>
       </c>
       <c r="M6">
-        <v>6.829337636</v>
+        <v>8.536672045</v>
       </c>
       <c r="N6">
-        <v>318.970662364</v>
+        <v>317.263327955</v>
       </c>
       <c r="O6">
-        <v>95.69119870920001</v>
+        <v>95.1789983865</v>
       </c>
       <c r="P6">
-        <v>223.2794636548</v>
+        <v>222.0843295685</v>
       </c>
       <c r="Q6">
-        <v>280.0794636548</v>
+        <v>278.8843295685</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1152240195891337</v>
+        <v>0.1157417780987479</v>
       </c>
       <c r="T6">
-        <v>1.010204075617023</v>
+        <v>1.017738092801467</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.70594417276809</v>
+        <v>38.16475533821448</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1117151891938105</v>
+        <v>0.1114069195820527</v>
       </c>
       <c r="C7">
-        <v>3268.272611617836</v>
+        <v>3243.319146320018</v>
       </c>
       <c r="D7">
-        <v>1913.187761617836</v>
+        <v>1922.177326320018</v>
       </c>
       <c r="E7">
-        <v>169.41215</v>
+        <v>203.35518</v>
       </c>
       <c r="F7">
-        <v>169.71515</v>
+        <v>203.65818</v>
       </c>
       <c r="G7">
         <v>1524.8</v>
@@ -1989,28 +1989,28 @@
         <v>325.8</v>
       </c>
       <c r="M7">
-        <v>8.536672045</v>
+        <v>10.244006454</v>
       </c>
       <c r="N7">
-        <v>317.263327955</v>
+        <v>315.555993546</v>
       </c>
       <c r="O7">
-        <v>95.1789983865</v>
+        <v>94.6667980638</v>
       </c>
       <c r="P7">
-        <v>222.0843295685</v>
+        <v>220.8891954822</v>
       </c>
       <c r="Q7">
-        <v>278.8843295685</v>
+        <v>277.6891954822</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1157417780987479</v>
+        <v>0.1162705527468646</v>
       </c>
       <c r="T7">
-        <v>1.017738092801467</v>
+        <v>1.025432408223878</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.16475533821448</v>
+        <v>31.80396278184539</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1114069195820527</v>
+        <v>0.111098649970295</v>
       </c>
       <c r="C8">
-        <v>3243.319146320018</v>
+        <v>3218.450559028769</v>
       </c>
       <c r="D8">
-        <v>1922.177326320018</v>
+        <v>1931.251769028769</v>
       </c>
       <c r="E8">
-        <v>203.35518</v>
+        <v>237.29821</v>
       </c>
       <c r="F8">
-        <v>203.65818</v>
+        <v>237.60121</v>
       </c>
       <c r="G8">
         <v>1524.8</v>
@@ -2071,28 +2071,28 @@
         <v>325.8</v>
       </c>
       <c r="M8">
-        <v>10.244006454</v>
+        <v>11.951340863</v>
       </c>
       <c r="N8">
-        <v>315.555993546</v>
+        <v>313.848659137</v>
       </c>
       <c r="O8">
-        <v>94.6667980638</v>
+        <v>94.15459774110001</v>
       </c>
       <c r="P8">
-        <v>220.8891954822</v>
+        <v>219.6940613959</v>
       </c>
       <c r="Q8">
-        <v>277.6891954822</v>
+        <v>276.4940613959</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1162705527468646</v>
+        <v>0.1168106988927903</v>
       </c>
       <c r="T8">
-        <v>1.025432408223878</v>
+        <v>1.033292192795158</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.8039627818454</v>
+        <v>27.26053952729606</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1110986499702949</v>
+        <v>0.1107903803585372</v>
       </c>
       <c r="C9">
-        <v>3218.45055902877</v>
+        <v>3193.66805755254</v>
       </c>
       <c r="D9">
-        <v>1931.25176902877</v>
+        <v>1940.41229755254</v>
       </c>
       <c r="E9">
-        <v>237.29821</v>
+        <v>271.24124</v>
       </c>
       <c r="F9">
-        <v>237.60121</v>
+        <v>271.54424</v>
       </c>
       <c r="G9">
         <v>1524.8</v>
@@ -2153,28 +2153,28 @@
         <v>325.8</v>
       </c>
       <c r="M9">
-        <v>11.951340863</v>
+        <v>13.658675272</v>
       </c>
       <c r="N9">
-        <v>313.848659137</v>
+        <v>312.141324728</v>
       </c>
       <c r="O9">
-        <v>94.15459774110001</v>
+        <v>93.64239741840001</v>
       </c>
       <c r="P9">
-        <v>219.6940613959</v>
+        <v>218.4989273096</v>
       </c>
       <c r="Q9">
-        <v>276.4940613959</v>
+        <v>275.2989273096</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1168106988927903</v>
+        <v>0.1173625873462361</v>
       </c>
       <c r="T9">
-        <v>1.033292192795158</v>
+        <v>1.041322842248422</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.26053952729605</v>
+        <v>23.85297208638405</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1107903803585372</v>
+        <v>0.1104821107467794</v>
       </c>
       <c r="C10">
-        <v>3193.66805755254</v>
+        <v>3168.972872725038</v>
       </c>
       <c r="D10">
-        <v>1940.41229755254</v>
+        <v>1949.660142725038</v>
       </c>
       <c r="E10">
-        <v>271.24124</v>
+        <v>305.18427</v>
       </c>
       <c r="F10">
-        <v>271.54424</v>
+        <v>305.48727</v>
       </c>
       <c r="G10">
         <v>1524.8</v>
@@ -2235,28 +2235,28 @@
         <v>325.8</v>
       </c>
       <c r="M10">
-        <v>13.658675272</v>
+        <v>15.366009681</v>
       </c>
       <c r="N10">
-        <v>312.141324728</v>
+        <v>310.433990319</v>
       </c>
       <c r="O10">
-        <v>93.64239741840001</v>
+        <v>93.13019709570001</v>
       </c>
       <c r="P10">
-        <v>218.4989273096</v>
+        <v>217.3037932233</v>
       </c>
       <c r="Q10">
-        <v>275.2989273096</v>
+        <v>274.1037932233</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1173625873462361</v>
+        <v>0.117926605216241</v>
       </c>
       <c r="T10">
-        <v>1.041322842248422</v>
+        <v>1.049529989491868</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.85297208638405</v>
+        <v>21.2026418545636</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1104821107467794</v>
+        <v>0.1101738411350216</v>
       </c>
       <c r="C11">
-        <v>3168.972872725038</v>
+        <v>3144.366258956545</v>
       </c>
       <c r="D11">
-        <v>1949.660142725038</v>
+        <v>1958.996558956545</v>
       </c>
       <c r="E11">
-        <v>305.18427</v>
+        <v>339.1273</v>
       </c>
       <c r="F11">
-        <v>305.48727</v>
+        <v>339.4303</v>
       </c>
       <c r="G11">
         <v>1524.8</v>
@@ -2317,28 +2317,28 @@
         <v>325.8</v>
       </c>
       <c r="M11">
-        <v>15.366009681</v>
+        <v>17.07334409</v>
       </c>
       <c r="N11">
-        <v>310.433990319</v>
+        <v>308.72665591</v>
       </c>
       <c r="O11">
-        <v>93.13019709570001</v>
+        <v>92.617996773</v>
       </c>
       <c r="P11">
-        <v>217.3037932233</v>
+        <v>216.108659137</v>
       </c>
       <c r="Q11">
-        <v>274.1037932233</v>
+        <v>272.908659137</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.117926605216241</v>
+        <v>0.1185031568166906</v>
       </c>
       <c r="T11">
-        <v>1.049529989491868</v>
+        <v>1.057919517785169</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.2026418545636</v>
+        <v>19.08237766910724</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1101738411350216</v>
+        <v>0.1098655715232638</v>
       </c>
       <c r="C12">
-        <v>3144.366258956545</v>
+        <v>3119.849494801143</v>
       </c>
       <c r="D12">
-        <v>1958.996558956545</v>
+        <v>1968.422824801143</v>
       </c>
       <c r="E12">
-        <v>339.1273</v>
+        <v>373.07033</v>
       </c>
       <c r="F12">
-        <v>339.4303</v>
+        <v>373.37333</v>
       </c>
       <c r="G12">
         <v>1524.8</v>
@@ -2399,28 +2399,28 @@
         <v>325.8</v>
       </c>
       <c r="M12">
-        <v>17.07334409</v>
+        <v>18.780678499</v>
       </c>
       <c r="N12">
-        <v>308.72665591</v>
+        <v>307.019321501</v>
       </c>
       <c r="O12">
-        <v>92.617996773</v>
+        <v>92.10579645030001</v>
       </c>
       <c r="P12">
-        <v>216.108659137</v>
+        <v>214.9135250507</v>
       </c>
       <c r="Q12">
-        <v>272.908659137</v>
+        <v>271.7135250507</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1185031568166906</v>
+        <v>0.1190926646328806</v>
       </c>
       <c r="T12">
-        <v>1.057919517785169</v>
+        <v>1.066497574804161</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.08237766910724</v>
+        <v>17.34761606282476</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1098655715232638</v>
+        <v>0.1095573019115059</v>
       </c>
       <c r="C13">
-        <v>3119.849494801143</v>
+        <v>3095.423883540395</v>
       </c>
       <c r="D13">
-        <v>1968.422824801143</v>
+        <v>1977.940243540394</v>
       </c>
       <c r="E13">
-        <v>373.07033</v>
+        <v>407.01336</v>
       </c>
       <c r="F13">
-        <v>373.37333</v>
+        <v>407.31636</v>
       </c>
       <c r="G13">
         <v>1524.8</v>
@@ -2481,28 +2481,28 @@
         <v>325.8</v>
       </c>
       <c r="M13">
-        <v>18.780678499</v>
+        <v>20.488012908</v>
       </c>
       <c r="N13">
-        <v>307.019321501</v>
+        <v>305.311987092</v>
       </c>
       <c r="O13">
-        <v>92.10579645030001</v>
+        <v>91.59359612760001</v>
       </c>
       <c r="P13">
-        <v>214.9135250507</v>
+        <v>213.7183909644</v>
       </c>
       <c r="Q13">
-        <v>271.7135250507</v>
+        <v>270.5183909644001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1190926646328806</v>
+        <v>0.119695570353984</v>
       </c>
       <c r="T13">
-        <v>1.066497574804161</v>
+        <v>1.075270587664494</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.34761606282476</v>
+        <v>15.9019813909227</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1095573019115059</v>
+        <v>0.1092490322997482</v>
       </c>
       <c r="C14">
-        <v>3095.423883540395</v>
+        <v>3071.090753784038</v>
       </c>
       <c r="D14">
-        <v>1977.940243540394</v>
+        <v>1987.550143784038</v>
       </c>
       <c r="E14">
-        <v>407.01336</v>
+        <v>440.95639</v>
       </c>
       <c r="F14">
-        <v>407.31636</v>
+        <v>441.25939</v>
       </c>
       <c r="G14">
         <v>1524.8</v>
@@ -2563,28 +2563,28 @@
         <v>325.8</v>
       </c>
       <c r="M14">
-        <v>20.488012908</v>
+        <v>22.195347317</v>
       </c>
       <c r="N14">
-        <v>305.311987092</v>
+        <v>303.604652683</v>
       </c>
       <c r="O14">
-        <v>91.59359612760001</v>
+        <v>91.08139580490001</v>
       </c>
       <c r="P14">
-        <v>213.7183909644</v>
+        <v>212.5232568781</v>
       </c>
       <c r="Q14">
-        <v>270.5183909644001</v>
+        <v>269.3232568781</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.119695570353984</v>
+        <v>0.120312335976722</v>
       </c>
       <c r="T14">
-        <v>1.075270587664494</v>
+        <v>1.084245278981387</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.9019813909227</v>
+        <v>14.67875205315941</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1092490322997482</v>
+        <v>0.1089407626879904</v>
       </c>
       <c r="C15">
-        <v>3071.090753784038</v>
+        <v>3046.851460088288</v>
       </c>
       <c r="D15">
-        <v>1987.550143784038</v>
+        <v>1997.253880088288</v>
       </c>
       <c r="E15">
-        <v>440.95639</v>
+        <v>474.89942</v>
       </c>
       <c r="F15">
-        <v>441.25939</v>
+        <v>475.20242</v>
       </c>
       <c r="G15">
         <v>1524.8</v>
@@ -2645,28 +2645,28 @@
         <v>325.8</v>
       </c>
       <c r="M15">
-        <v>22.195347317</v>
+        <v>23.902681726</v>
       </c>
       <c r="N15">
-        <v>303.604652683</v>
+        <v>301.897318274</v>
       </c>
       <c r="O15">
-        <v>91.08139580490001</v>
+        <v>90.56919548219999</v>
       </c>
       <c r="P15">
-        <v>212.5232568781</v>
+        <v>211.3281227918</v>
       </c>
       <c r="Q15">
-        <v>269.3232568781</v>
+        <v>268.1281227918</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.120312335976722</v>
+        <v>0.1209434449860353</v>
       </c>
       <c r="T15">
-        <v>1.084245278981387</v>
+        <v>1.093428684049835</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.67875205315941</v>
+        <v>13.63026976364803</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1089407626879904</v>
+        <v>0.1087899930762326</v>
       </c>
       <c r="C16">
-        <v>3046.851460088288</v>
+        <v>3017.688954380745</v>
       </c>
       <c r="D16">
-        <v>1997.253880088288</v>
+        <v>2002.034404380745</v>
       </c>
       <c r="E16">
-        <v>474.89942</v>
+        <v>508.84245</v>
       </c>
       <c r="F16">
-        <v>475.20242</v>
+        <v>509.14545</v>
       </c>
       <c r="G16">
         <v>1524.8</v>
@@ -2727,45 +2727,45 @@
         <v>325.8</v>
       </c>
       <c r="M16">
-        <v>23.902681726</v>
+        <v>26.37373431</v>
       </c>
       <c r="N16">
-        <v>301.897318274</v>
+        <v>299.42626569</v>
       </c>
       <c r="O16">
-        <v>90.56919548219999</v>
+        <v>89.82787970700001</v>
       </c>
       <c r="P16">
-        <v>211.3281227918</v>
+        <v>209.598385983</v>
       </c>
       <c r="Q16">
-        <v>268.1281227918</v>
+        <v>266.398385983</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1209434449860353</v>
+        <v>0.1215894036190971</v>
       </c>
       <c r="T16">
-        <v>1.093428684049835</v>
+        <v>1.102828169237541</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.63026976364803</v>
+        <v>12.35319944345038</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1087899930762326</v>
+        <v>0.1084922234644748</v>
       </c>
       <c r="C17">
-        <v>3017.688954380745</v>
+        <v>2993.25499862272</v>
       </c>
       <c r="D17">
-        <v>2002.034404380745</v>
+        <v>2011.54347862272</v>
       </c>
       <c r="E17">
-        <v>508.84245</v>
+        <v>542.78548</v>
       </c>
       <c r="F17">
-        <v>509.14545</v>
+        <v>543.08848</v>
       </c>
       <c r="G17">
         <v>1524.8</v>
@@ -2809,28 +2809,28 @@
         <v>325.8</v>
       </c>
       <c r="M17">
-        <v>26.37373431</v>
+        <v>28.131983264</v>
       </c>
       <c r="N17">
-        <v>299.42626569</v>
+        <v>297.668016736</v>
       </c>
       <c r="O17">
-        <v>89.82787970700001</v>
+        <v>89.3004050208</v>
       </c>
       <c r="P17">
-        <v>209.598385983</v>
+        <v>208.3676117152</v>
       </c>
       <c r="Q17">
-        <v>266.398385983</v>
+        <v>265.1676117152001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1215894036190971</v>
+        <v>0.1222507422196128</v>
       </c>
       <c r="T17">
-        <v>1.102828169237541</v>
+        <v>1.112451451691621</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.35319944345038</v>
+        <v>11.58112447823473</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1084922234644748</v>
+        <v>0.108194453852717</v>
       </c>
       <c r="C18">
-        <v>2993.25499862272</v>
+        <v>2968.911804564506</v>
       </c>
       <c r="D18">
-        <v>2011.54347862272</v>
+        <v>2021.143314564506</v>
       </c>
       <c r="E18">
-        <v>542.78548</v>
+        <v>576.72851</v>
       </c>
       <c r="F18">
-        <v>543.08848</v>
+        <v>577.03151</v>
       </c>
       <c r="G18">
         <v>1524.8</v>
@@ -2891,28 +2891,28 @@
         <v>325.8</v>
       </c>
       <c r="M18">
-        <v>28.131983264</v>
+        <v>29.890232218</v>
       </c>
       <c r="N18">
-        <v>297.668016736</v>
+        <v>295.909767782</v>
       </c>
       <c r="O18">
-        <v>89.3004050208</v>
+        <v>88.77293033460001</v>
       </c>
       <c r="P18">
-        <v>208.3676117152</v>
+        <v>207.1368374474</v>
       </c>
       <c r="Q18">
-        <v>265.1676117152001</v>
+        <v>263.9368374474</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1222507422196128</v>
+        <v>0.1229280166900205</v>
       </c>
       <c r="T18">
-        <v>1.112451451691621</v>
+        <v>1.122306620469895</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.58112447823473</v>
+        <v>10.89988186186798</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.108194453852717</v>
+        <v>0.1078966842409592</v>
       </c>
       <c r="C19">
-        <v>2968.911804564506</v>
+        <v>2944.66067788336</v>
       </c>
       <c r="D19">
-        <v>2021.143314564506</v>
+        <v>2030.83521788336</v>
       </c>
       <c r="E19">
-        <v>576.72851</v>
+        <v>610.67154</v>
       </c>
       <c r="F19">
-        <v>577.03151</v>
+        <v>610.97454</v>
       </c>
       <c r="G19">
         <v>1524.8</v>
@@ -2973,28 +2973,28 @@
         <v>325.8</v>
       </c>
       <c r="M19">
-        <v>29.890232218</v>
+        <v>31.648481172</v>
       </c>
       <c r="N19">
-        <v>295.909767782</v>
+        <v>294.151518828</v>
       </c>
       <c r="O19">
-        <v>88.77293033460001</v>
+        <v>88.2454556484</v>
       </c>
       <c r="P19">
-        <v>207.1368374474</v>
+        <v>205.9060631796</v>
       </c>
       <c r="Q19">
-        <v>263.9368374474</v>
+        <v>262.7060631796001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1229280166900205</v>
+        <v>0.1236218100499502</v>
       </c>
       <c r="T19">
-        <v>1.122306620469895</v>
+        <v>1.132402159218371</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.89988186186798</v>
+        <v>10.29433286954198</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1078966842409592</v>
+        <v>0.1078250146292014</v>
       </c>
       <c r="C20">
-        <v>2944.66067788336</v>
+        <v>2913.064268395743</v>
       </c>
       <c r="D20">
-        <v>2030.83521788336</v>
+        <v>2033.181838395743</v>
       </c>
       <c r="E20">
-        <v>610.6715399999999</v>
+        <v>644.61457</v>
       </c>
       <c r="F20">
-        <v>610.9745399999999</v>
+        <v>644.91757</v>
       </c>
       <c r="G20">
         <v>1524.8</v>
@@ -3055,45 +3055,45 @@
         <v>325.8</v>
       </c>
       <c r="M20">
-        <v>31.648481172</v>
+        <v>34.503089995</v>
       </c>
       <c r="N20">
-        <v>294.151518828</v>
+        <v>291.296910005</v>
       </c>
       <c r="O20">
-        <v>88.2454556484</v>
+        <v>87.38907300150001</v>
       </c>
       <c r="P20">
-        <v>205.9060631796</v>
+        <v>203.9078370035</v>
       </c>
       <c r="Q20">
-        <v>262.7060631796001</v>
+        <v>260.7078370035</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1236218100499502</v>
+        <v>0.1243327341101252</v>
       </c>
       <c r="T20">
-        <v>1.132402159218371</v>
+        <v>1.142746970528538</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.29433286954198</v>
+        <v>9.442632530802697</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1078250146292014</v>
+        <v>0.1075391450174436</v>
       </c>
       <c r="C21">
-        <v>2913.064268395743</v>
+        <v>2888.535442343838</v>
       </c>
       <c r="D21">
-        <v>2033.181838395743</v>
+        <v>2042.596042343838</v>
       </c>
       <c r="E21">
-        <v>644.61457</v>
+        <v>678.5576</v>
       </c>
       <c r="F21">
-        <v>644.91757</v>
+        <v>678.8606</v>
       </c>
       <c r="G21">
         <v>1524.8</v>
@@ -3137,28 +3137,28 @@
         <v>325.8</v>
       </c>
       <c r="M21">
-        <v>34.503089995</v>
+        <v>36.3190421</v>
       </c>
       <c r="N21">
-        <v>291.296910005</v>
+        <v>289.4809579</v>
       </c>
       <c r="O21">
-        <v>87.38907300150001</v>
+        <v>86.84428737</v>
       </c>
       <c r="P21">
-        <v>203.9078370035</v>
+        <v>202.63667053</v>
       </c>
       <c r="Q21">
-        <v>260.7078370035</v>
+        <v>259.43667053</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1243327341101252</v>
+        <v>0.1250614312718045</v>
       </c>
       <c r="T21">
-        <v>1.142746970528538</v>
+        <v>1.15335040212146</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.442632530802697</v>
+        <v>8.970500904262561</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1075391450174436</v>
+        <v>0.1072532754056858</v>
       </c>
       <c r="C22">
-        <v>2888.535442343838</v>
+        <v>2864.094202667431</v>
       </c>
       <c r="D22">
-        <v>2042.596042343838</v>
+        <v>2052.097832667431</v>
       </c>
       <c r="E22">
-        <v>678.5576</v>
+        <v>712.50063</v>
       </c>
       <c r="F22">
-        <v>678.8606</v>
+        <v>712.80363</v>
       </c>
       <c r="G22">
         <v>1524.8</v>
@@ -3219,28 +3219,28 @@
         <v>325.8</v>
       </c>
       <c r="M22">
-        <v>36.3190421</v>
+        <v>38.134994205</v>
       </c>
       <c r="N22">
-        <v>289.4809579</v>
+        <v>287.665005795</v>
       </c>
       <c r="O22">
-        <v>86.84428737</v>
+        <v>86.2995017385</v>
       </c>
       <c r="P22">
-        <v>202.63667053</v>
+        <v>201.3655040565</v>
       </c>
       <c r="Q22">
-        <v>259.43667053</v>
+        <v>258.1655040565</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1250614312718045</v>
+        <v>0.1258085764628934</v>
       </c>
       <c r="T22">
-        <v>1.15335040212146</v>
+        <v>1.164222275020531</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.970500904262561</v>
+        <v>8.543334194535772</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1072532754056858</v>
+        <v>0.106967405793928</v>
       </c>
       <c r="C23">
-        <v>2864.094202667431</v>
+        <v>2839.74177738737</v>
       </c>
       <c r="D23">
-        <v>2052.097832667431</v>
+        <v>2061.68843738737</v>
       </c>
       <c r="E23">
-        <v>712.50063</v>
+        <v>746.44366</v>
       </c>
       <c r="F23">
-        <v>712.80363</v>
+        <v>746.74666</v>
       </c>
       <c r="G23">
         <v>1524.8</v>
@@ -3301,28 +3301,28 @@
         <v>325.8</v>
       </c>
       <c r="M23">
-        <v>38.134994205</v>
+        <v>39.95094631</v>
       </c>
       <c r="N23">
-        <v>287.665005795</v>
+        <v>285.84905369</v>
       </c>
       <c r="O23">
-        <v>86.2995017385</v>
+        <v>85.75471610699999</v>
       </c>
       <c r="P23">
-        <v>201.3655040565</v>
+        <v>200.094337583</v>
       </c>
       <c r="Q23">
-        <v>258.1655040565</v>
+        <v>256.894337583</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1258085764628934</v>
+        <v>0.1265748792229846</v>
       </c>
       <c r="T23">
-        <v>1.164222275020531</v>
+        <v>1.175372913891373</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.543334194535772</v>
+        <v>8.155000822056873</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.106967405793928</v>
+        <v>0.1066815361821702</v>
       </c>
       <c r="C24">
-        <v>2839.74177738737</v>
+        <v>2815.479417589218</v>
       </c>
       <c r="D24">
-        <v>2061.68843738737</v>
+        <v>2071.369107589218</v>
       </c>
       <c r="E24">
-        <v>746.44366</v>
+        <v>780.38669</v>
       </c>
       <c r="F24">
-        <v>746.74666</v>
+        <v>780.68969</v>
       </c>
       <c r="G24">
         <v>1524.8</v>
@@ -3383,28 +3383,28 @@
         <v>325.8</v>
       </c>
       <c r="M24">
-        <v>39.95094631</v>
+        <v>41.766898415</v>
       </c>
       <c r="N24">
-        <v>285.84905369</v>
+        <v>284.033101585</v>
       </c>
       <c r="O24">
-        <v>85.75471610699999</v>
+        <v>85.2099304755</v>
       </c>
       <c r="P24">
-        <v>200.094337583</v>
+        <v>198.8231711095</v>
       </c>
       <c r="Q24">
-        <v>256.894337583</v>
+        <v>255.6231711095</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1265748792229846</v>
+        <v>0.1273610859508704</v>
       </c>
       <c r="T24">
-        <v>1.175372913891373</v>
+        <v>1.186813179745873</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.155000822056873</v>
+        <v>7.800435568923965</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1066815361821702</v>
+        <v>0.1065300665704124</v>
       </c>
       <c r="C25">
-        <v>2815.479417589218</v>
+        <v>2786.70268316984</v>
       </c>
       <c r="D25">
-        <v>2071.369107589218</v>
+        <v>2076.53540316984</v>
       </c>
       <c r="E25">
-        <v>780.38669</v>
+        <v>814.3297200000001</v>
       </c>
       <c r="F25">
-        <v>780.68969</v>
+        <v>814.6327200000001</v>
       </c>
       <c r="G25">
         <v>1524.8</v>
@@ -3465,45 +3465,45 @@
         <v>325.8</v>
       </c>
       <c r="M25">
-        <v>41.766898415</v>
+        <v>44.23455669600001</v>
       </c>
       <c r="N25">
-        <v>284.033101585</v>
+        <v>281.565443304</v>
       </c>
       <c r="O25">
-        <v>85.2099304755</v>
+        <v>84.46963299119999</v>
       </c>
       <c r="P25">
-        <v>198.8231711095</v>
+        <v>197.0958103128</v>
       </c>
       <c r="Q25">
-        <v>255.6231711095</v>
+        <v>253.8958103128</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1273610859508704</v>
+        <v>0.12816798232949</v>
       </c>
       <c r="T25">
-        <v>1.186813179745873</v>
+        <v>1.198554505228124</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.800435568923965</v>
+        <v>7.365282356937491</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1065300665704124</v>
+        <v>0.1062497969586546</v>
       </c>
       <c r="C26">
-        <v>2786.70268316984</v>
+        <v>2762.387307860655</v>
       </c>
       <c r="D26">
-        <v>2076.53540316984</v>
+        <v>2086.163057860655</v>
       </c>
       <c r="E26">
-        <v>814.32972</v>
+        <v>848.27275</v>
       </c>
       <c r="F26">
-        <v>814.6327199999999</v>
+        <v>848.57575</v>
       </c>
       <c r="G26">
         <v>1524.8</v>
@@ -3547,28 +3547,28 @@
         <v>325.8</v>
       </c>
       <c r="M26">
-        <v>44.234556696</v>
+        <v>46.077663225</v>
       </c>
       <c r="N26">
-        <v>281.565443304</v>
+        <v>279.722336775</v>
       </c>
       <c r="O26">
-        <v>84.46963299120002</v>
+        <v>83.9167010325</v>
       </c>
       <c r="P26">
-        <v>197.0958103128</v>
+        <v>195.8056357425</v>
       </c>
       <c r="Q26">
-        <v>253.8958103128001</v>
+        <v>252.6056357425001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.12816798232949</v>
+        <v>0.1289963959448728</v>
       </c>
       <c r="T26">
-        <v>1.198554505228124</v>
+        <v>1.210608932723234</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.365282356937493</v>
+        <v>7.070671062659993</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1062497969586546</v>
+        <v>0.1059695273468968</v>
       </c>
       <c r="C27">
-        <v>2762.387307860655</v>
+        <v>2738.161623767649</v>
       </c>
       <c r="D27">
-        <v>2086.163057860655</v>
+        <v>2095.880403767648</v>
       </c>
       <c r="E27">
-        <v>848.27275</v>
+        <v>882.21578</v>
       </c>
       <c r="F27">
-        <v>848.57575</v>
+        <v>882.51878</v>
       </c>
       <c r="G27">
         <v>1524.8</v>
@@ -3629,28 +3629,28 @@
         <v>325.8</v>
       </c>
       <c r="M27">
-        <v>46.077663225</v>
+        <v>47.920769754</v>
       </c>
       <c r="N27">
-        <v>279.722336775</v>
+        <v>277.879230246</v>
       </c>
       <c r="O27">
-        <v>83.9167010325</v>
+        <v>83.3637690738</v>
       </c>
       <c r="P27">
-        <v>195.8056357425</v>
+        <v>194.5154611722</v>
       </c>
       <c r="Q27">
-        <v>252.6056357425001</v>
+        <v>251.3154611722</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1289963959448728</v>
+        <v>0.1298471991174281</v>
       </c>
       <c r="T27">
-        <v>1.210608932723234</v>
+        <v>1.22298915555605</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.070671062659993</v>
+        <v>6.798722175634609</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1059695273468968</v>
+        <v>0.105689257735139</v>
       </c>
       <c r="C28">
-        <v>2738.161623767649</v>
+        <v>2714.026890101067</v>
       </c>
       <c r="D28">
-        <v>2095.880403767648</v>
+        <v>2105.688700101067</v>
       </c>
       <c r="E28">
-        <v>882.21578</v>
+        <v>916.15881</v>
       </c>
       <c r="F28">
-        <v>882.51878</v>
+        <v>916.46181</v>
       </c>
       <c r="G28">
         <v>1524.8</v>
@@ -3711,28 +3711,28 @@
         <v>325.8</v>
       </c>
       <c r="M28">
-        <v>47.920769754</v>
+        <v>49.763876283</v>
       </c>
       <c r="N28">
-        <v>277.879230246</v>
+        <v>276.036123717</v>
       </c>
       <c r="O28">
-        <v>83.3637690738</v>
+        <v>82.8108371151</v>
       </c>
       <c r="P28">
-        <v>194.5154611722</v>
+        <v>193.2252866019</v>
       </c>
       <c r="Q28">
-        <v>251.3154611722</v>
+        <v>250.0252866019</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1298471991174281</v>
+        <v>0.1307213119659438</v>
       </c>
       <c r="T28">
-        <v>1.22298915555605</v>
+        <v>1.235708562576067</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.798722175634609</v>
+        <v>6.546917650611104</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.105689257735139</v>
+        <v>0.1054089881233812</v>
       </c>
       <c r="C29">
-        <v>2714.026890101067</v>
+        <v>2689.984389753383</v>
       </c>
       <c r="D29">
-        <v>2105.688700101067</v>
+        <v>2115.589229753383</v>
       </c>
       <c r="E29">
-        <v>916.15881</v>
+        <v>950.10184</v>
       </c>
       <c r="F29">
-        <v>916.46181</v>
+        <v>950.40484</v>
       </c>
       <c r="G29">
         <v>1524.8</v>
@@ -3793,28 +3793,28 @@
         <v>325.8</v>
       </c>
       <c r="M29">
-        <v>49.763876283</v>
+        <v>51.60698281200001</v>
       </c>
       <c r="N29">
-        <v>276.036123717</v>
+        <v>274.193017188</v>
       </c>
       <c r="O29">
-        <v>82.8108371151</v>
+        <v>82.2579051564</v>
       </c>
       <c r="P29">
-        <v>193.2252866019</v>
+        <v>191.9351120316</v>
       </c>
       <c r="Q29">
-        <v>250.0252866019</v>
+        <v>248.7351120316</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1307213119659438</v>
+        <v>0.1316197057269183</v>
       </c>
       <c r="T29">
-        <v>1.235708562576067</v>
+        <v>1.248781286457751</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.546917650611104</v>
+        <v>6.313099163089278</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1054089881233812</v>
+        <v>0.1053317185116234</v>
       </c>
       <c r="C30">
-        <v>2689.984389753383</v>
+        <v>2658.787303638576</v>
       </c>
       <c r="D30">
-        <v>2115.589229753383</v>
+        <v>2118.335173638576</v>
       </c>
       <c r="E30">
-        <v>950.10184</v>
+        <v>984.0448700000001</v>
       </c>
       <c r="F30">
-        <v>950.40484</v>
+        <v>984.3478700000001</v>
       </c>
       <c r="G30">
         <v>1524.8</v>
@@ -3875,45 +3875,45 @@
         <v>325.8</v>
       </c>
       <c r="M30">
-        <v>51.60698281200001</v>
+        <v>54.434437211</v>
       </c>
       <c r="N30">
-        <v>274.193017188</v>
+        <v>271.365562789</v>
       </c>
       <c r="O30">
-        <v>82.2579051564</v>
+        <v>81.40966883670001</v>
       </c>
       <c r="P30">
-        <v>191.9351120316</v>
+        <v>189.9558939523</v>
       </c>
       <c r="Q30">
-        <v>248.7351120316</v>
+        <v>246.7558939523</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1316197057269183</v>
+        <v>0.1325434063543992</v>
       </c>
       <c r="T30">
-        <v>1.248781286457751</v>
+        <v>1.26222225608258</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.313099163089278</v>
+        <v>5.985181746935798</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1053317185116234</v>
+        <v>0.1050584488998656</v>
       </c>
       <c r="C31">
-        <v>2658.787303638576</v>
+        <v>2634.612950362654</v>
       </c>
       <c r="D31">
-        <v>2118.335173638576</v>
+        <v>2128.103850362655</v>
       </c>
       <c r="E31">
-        <v>984.0448699999999</v>
+        <v>1017.9879</v>
       </c>
       <c r="F31">
-        <v>984.3478699999999</v>
+        <v>1018.2909</v>
       </c>
       <c r="G31">
         <v>1524.8</v>
@@ -3957,28 +3957,28 @@
         <v>325.8</v>
       </c>
       <c r="M31">
-        <v>54.434437211</v>
+        <v>56.31148677</v>
       </c>
       <c r="N31">
-        <v>271.365562789</v>
+        <v>269.48851323</v>
       </c>
       <c r="O31">
-        <v>81.40966883670001</v>
+        <v>80.846553969</v>
       </c>
       <c r="P31">
-        <v>189.9558939523</v>
+        <v>188.641959261</v>
       </c>
       <c r="Q31">
-        <v>246.7558939523</v>
+        <v>245.441959261</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1325434063543992</v>
+        <v>0.1334934984283794</v>
       </c>
       <c r="T31">
-        <v>1.26222225608258</v>
+        <v>1.276047253410977</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.985181746935798</v>
+        <v>5.785675688704605</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1050584488998656</v>
+        <v>0.1047851792881078</v>
       </c>
       <c r="C32">
-        <v>2634.612950362654</v>
+        <v>2610.529110755692</v>
       </c>
       <c r="D32">
-        <v>2128.103850362655</v>
+        <v>2137.963040755692</v>
       </c>
       <c r="E32">
-        <v>1017.9879</v>
+        <v>1051.93093</v>
       </c>
       <c r="F32">
-        <v>1018.2909</v>
+        <v>1052.23393</v>
       </c>
       <c r="G32">
         <v>1524.8</v>
@@ -4039,28 +4039,28 @@
         <v>325.8</v>
       </c>
       <c r="M32">
-        <v>56.31148677</v>
+        <v>58.18853632899999</v>
       </c>
       <c r="N32">
-        <v>269.48851323</v>
+        <v>267.611463671</v>
       </c>
       <c r="O32">
-        <v>80.846553969</v>
+        <v>80.2834391013</v>
       </c>
       <c r="P32">
-        <v>188.641959261</v>
+        <v>187.3280245697</v>
       </c>
       <c r="Q32">
-        <v>245.441959261</v>
+        <v>244.1280245697</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1334934984283794</v>
+        <v>0.1344711294030548</v>
       </c>
       <c r="T32">
-        <v>1.276047253410977</v>
+        <v>1.290272975299616</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.785675688704605</v>
+        <v>5.599040989068973</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1047851792881078</v>
+        <v>0.10451190967635</v>
       </c>
       <c r="C33">
-        <v>2610.529110755692</v>
+        <v>2586.537048682309</v>
       </c>
       <c r="D33">
-        <v>2137.963040755692</v>
+        <v>2147.914008682309</v>
       </c>
       <c r="E33">
-        <v>1051.93093</v>
+        <v>1085.87396</v>
       </c>
       <c r="F33">
-        <v>1052.23393</v>
+        <v>1086.17696</v>
       </c>
       <c r="G33">
         <v>1524.8</v>
@@ -4121,28 +4121,28 @@
         <v>325.8</v>
       </c>
       <c r="M33">
-        <v>58.18853632899999</v>
+        <v>60.065585888</v>
       </c>
       <c r="N33">
-        <v>267.611463671</v>
+        <v>265.734414112</v>
       </c>
       <c r="O33">
-        <v>80.2834391013</v>
+        <v>79.72032423360001</v>
       </c>
       <c r="P33">
-        <v>187.3280245697</v>
+        <v>186.0140898784</v>
       </c>
       <c r="Q33">
-        <v>244.1280245697</v>
+        <v>242.8140898784</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1344711294030548</v>
+        <v>0.1354775142299265</v>
       </c>
       <c r="T33">
-        <v>1.290272975299616</v>
+        <v>1.304917100773216</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.599040989068973</v>
+        <v>5.424070958160567</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.10451190967635</v>
+        <v>0.1042386400645922</v>
       </c>
       <c r="C34">
-        <v>2586.537048682309</v>
+        <v>2562.638051647363</v>
       </c>
       <c r="D34">
-        <v>2147.914008682309</v>
+        <v>2157.958041647363</v>
       </c>
       <c r="E34">
-        <v>1085.87396</v>
+        <v>1119.81699</v>
       </c>
       <c r="F34">
-        <v>1086.17696</v>
+        <v>1120.11999</v>
       </c>
       <c r="G34">
         <v>1524.8</v>
@@ -4203,28 +4203,28 @@
         <v>325.8</v>
       </c>
       <c r="M34">
-        <v>60.065585888</v>
+        <v>61.942635447</v>
       </c>
       <c r="N34">
-        <v>265.734414112</v>
+        <v>263.857364553</v>
       </c>
       <c r="O34">
-        <v>79.72032423360001</v>
+        <v>79.1572093659</v>
       </c>
       <c r="P34">
-        <v>186.0140898784</v>
+        <v>184.7001551871</v>
       </c>
       <c r="Q34">
-        <v>242.8140898784</v>
+        <v>241.5001551871</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1354775142299265</v>
+        <v>0.1365139403949137</v>
       </c>
       <c r="T34">
-        <v>1.304917100773216</v>
+        <v>1.319998364320655</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.424070958160567</v>
+        <v>5.259705171549641</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1042386400645922</v>
+        <v>0.1039653704528344</v>
       </c>
       <c r="C35">
-        <v>2562.638051647363</v>
+        <v>2538.833431351275</v>
       </c>
       <c r="D35">
-        <v>2157.958041647363</v>
+        <v>2168.096451351275</v>
       </c>
       <c r="E35">
-        <v>1119.81699</v>
+        <v>1153.76002</v>
       </c>
       <c r="F35">
-        <v>1120.11999</v>
+        <v>1154.06302</v>
       </c>
       <c r="G35">
         <v>1524.8</v>
@@ -4285,28 +4285,28 @@
         <v>325.8</v>
       </c>
       <c r="M35">
-        <v>61.942635447</v>
+        <v>63.81968500600001</v>
       </c>
       <c r="N35">
-        <v>263.857364553</v>
+        <v>261.980314994</v>
       </c>
       <c r="O35">
-        <v>79.1572093659</v>
+        <v>78.59409449820001</v>
       </c>
       <c r="P35">
-        <v>184.7001551871</v>
+        <v>183.3862204958</v>
       </c>
       <c r="Q35">
-        <v>241.5001551871</v>
+        <v>240.1862204958</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1365139403949137</v>
+        <v>0.1375817734133855</v>
       </c>
       <c r="T35">
-        <v>1.319998364320655</v>
+        <v>1.335536635854379</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.259705171549641</v>
+        <v>5.10500796062171</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1039653704528344</v>
+        <v>0.1036921008410766</v>
       </c>
       <c r="C36">
-        <v>2538.833431351275</v>
+        <v>2515.124524261078</v>
       </c>
       <c r="D36">
-        <v>2168.096451351275</v>
+        <v>2178.330574261077</v>
       </c>
       <c r="E36">
-        <v>1153.76002</v>
+        <v>1187.70305</v>
       </c>
       <c r="F36">
-        <v>1154.06302</v>
+        <v>1188.00605</v>
       </c>
       <c r="G36">
         <v>1524.8</v>
@@ -4367,28 +4367,28 @@
         <v>325.8</v>
       </c>
       <c r="M36">
-        <v>63.81968500600001</v>
+        <v>65.696734565</v>
       </c>
       <c r="N36">
-        <v>261.980314994</v>
+        <v>260.103265435</v>
       </c>
       <c r="O36">
-        <v>78.59409449820001</v>
+        <v>78.0309796305</v>
       </c>
       <c r="P36">
-        <v>183.3862204958</v>
+        <v>182.0722858045</v>
       </c>
       <c r="Q36">
-        <v>240.1862204958</v>
+        <v>238.8722858045001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1375817734133855</v>
+        <v>0.1386824628324255</v>
       </c>
       <c r="T36">
-        <v>1.335536635854379</v>
+        <v>1.351553008050679</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.10500796062171</v>
+        <v>4.959150590318233</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1036921008410766</v>
+        <v>0.1034188312293188</v>
       </c>
       <c r="C37">
-        <v>2515.124524261078</v>
+        <v>2491.512692197726</v>
       </c>
       <c r="D37">
-        <v>2178.330574261077</v>
+        <v>2188.661772197726</v>
       </c>
       <c r="E37">
-        <v>1187.70305</v>
+        <v>1221.64608</v>
       </c>
       <c r="F37">
-        <v>1188.00605</v>
+        <v>1221.94908</v>
       </c>
       <c r="G37">
         <v>1524.8</v>
@@ -4449,28 +4449,28 @@
         <v>325.8</v>
       </c>
       <c r="M37">
-        <v>65.696734565</v>
+        <v>67.57378412400001</v>
       </c>
       <c r="N37">
-        <v>260.103265435</v>
+        <v>258.226215876</v>
       </c>
       <c r="O37">
-        <v>78.0309796305</v>
+        <v>77.46786476279999</v>
       </c>
       <c r="P37">
-        <v>182.0722858045</v>
+        <v>180.7583511132</v>
       </c>
       <c r="Q37">
-        <v>238.8722858045001</v>
+        <v>237.5583511132</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1386824628324255</v>
+        <v>0.1398175487958106</v>
       </c>
       <c r="T37">
-        <v>1.351553008050679</v>
+        <v>1.368069891878114</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.959150590318233</v>
+        <v>4.821396407253836</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1034188312293188</v>
+        <v>0.103145561617561</v>
       </c>
       <c r="C38">
-        <v>2491.512692197726</v>
+        <v>2467.999322940196</v>
       </c>
       <c r="D38">
-        <v>2188.661772197725</v>
+        <v>2199.091432940196</v>
       </c>
       <c r="E38">
-        <v>1221.64608</v>
+        <v>1255.58911</v>
       </c>
       <c r="F38">
-        <v>1221.94908</v>
+        <v>1255.89211</v>
       </c>
       <c r="G38">
         <v>1524.8</v>
@@ -4531,28 +4531,28 @@
         <v>325.8</v>
       </c>
       <c r="M38">
-        <v>67.573784124</v>
+        <v>69.450833683</v>
       </c>
       <c r="N38">
-        <v>258.226215876</v>
+        <v>256.349166317</v>
       </c>
       <c r="O38">
-        <v>77.4678647628</v>
+        <v>76.90474989510001</v>
       </c>
       <c r="P38">
-        <v>180.7583511132</v>
+        <v>179.4444164219</v>
       </c>
       <c r="Q38">
-        <v>237.5583511132</v>
+        <v>236.2444164219</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1398175487958106</v>
+        <v>0.1409886692342238</v>
       </c>
       <c r="T38">
-        <v>1.368069891878114</v>
+        <v>1.38511112122388</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.821396407253838</v>
+        <v>4.691088396246977</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.103145561617561</v>
+        <v>0.1028722920058032</v>
       </c>
       <c r="C39">
-        <v>2467.999322940196</v>
+        <v>2444.585830846934</v>
       </c>
       <c r="D39">
-        <v>2199.091432940196</v>
+        <v>2209.620970846934</v>
       </c>
       <c r="E39">
-        <v>1255.58911</v>
+        <v>1289.53214</v>
       </c>
       <c r="F39">
-        <v>1255.89211</v>
+        <v>1289.83514</v>
       </c>
       <c r="G39">
         <v>1524.8</v>
@@ -4613,28 +4613,28 @@
         <v>325.8</v>
       </c>
       <c r="M39">
-        <v>69.450833683</v>
+        <v>71.327883242</v>
       </c>
       <c r="N39">
-        <v>256.349166317</v>
+        <v>254.472116758</v>
       </c>
       <c r="O39">
-        <v>76.90474989510001</v>
+        <v>76.3416350274</v>
       </c>
       <c r="P39">
-        <v>179.4444164219</v>
+        <v>178.1304817306</v>
       </c>
       <c r="Q39">
-        <v>236.2444164219</v>
+        <v>234.9304817306</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1409886692342238</v>
+        <v>0.1421975677512955</v>
       </c>
       <c r="T39">
-        <v>1.38511112122388</v>
+        <v>1.402702067645317</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.691088396246977</v>
+        <v>4.5676387016089</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1028722920058032</v>
+        <v>0.1032815223940454</v>
       </c>
       <c r="C40">
-        <v>2444.585830846934</v>
+        <v>2394.911762243449</v>
       </c>
       <c r="D40">
-        <v>2209.620970846934</v>
+        <v>2193.889932243449</v>
       </c>
       <c r="E40">
-        <v>1289.53214</v>
+        <v>1323.47517</v>
       </c>
       <c r="F40">
-        <v>1289.83514</v>
+        <v>1323.77817</v>
       </c>
       <c r="G40">
         <v>1524.8</v>
@@ -4695,45 +4695,45 @@
         <v>325.8</v>
       </c>
       <c r="M40">
-        <v>71.327883242</v>
+        <v>76.51437822600001</v>
       </c>
       <c r="N40">
-        <v>254.472116758</v>
+        <v>249.285621774</v>
       </c>
       <c r="O40">
-        <v>76.3416350274</v>
+        <v>74.78568653219999</v>
       </c>
       <c r="P40">
-        <v>178.1304817306</v>
+        <v>174.4999352418</v>
       </c>
       <c r="Q40">
-        <v>234.9304817306</v>
+        <v>231.2999352418</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1421975677512955</v>
+        <v>0.1434461022853203</v>
       </c>
       <c r="T40">
-        <v>1.402702067645317</v>
+        <v>1.420869766408439</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.5676387016089</v>
+        <v>4.258023231106796</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1032815223940454</v>
+        <v>0.1030257527822876</v>
       </c>
       <c r="C41">
-        <v>2394.911762243449</v>
+        <v>2370.77428916367</v>
       </c>
       <c r="D41">
-        <v>2193.889932243449</v>
+        <v>2203.69548916367</v>
       </c>
       <c r="E41">
-        <v>1323.47517</v>
+        <v>1357.4182</v>
       </c>
       <c r="F41">
-        <v>1323.77817</v>
+        <v>1357.7212</v>
       </c>
       <c r="G41">
         <v>1524.8</v>
@@ -4777,28 +4777,28 @@
         <v>325.8</v>
       </c>
       <c r="M41">
-        <v>76.51437822600001</v>
+        <v>78.47628536000001</v>
       </c>
       <c r="N41">
-        <v>249.285621774</v>
+        <v>247.32371464</v>
       </c>
       <c r="O41">
-        <v>74.78568653219999</v>
+        <v>74.19711439199999</v>
       </c>
       <c r="P41">
-        <v>174.4999352418</v>
+        <v>173.126600248</v>
       </c>
       <c r="Q41">
-        <v>231.2999352418</v>
+        <v>229.926600248</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1434461022853203</v>
+        <v>0.144736254637146</v>
       </c>
       <c r="T41">
-        <v>1.420869766408439</v>
+        <v>1.439643055130333</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.258023231106796</v>
+        <v>4.151572650329125</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1030257527822876</v>
+        <v>0.1027699831705298</v>
       </c>
       <c r="C42">
-        <v>2370.77428916367</v>
+        <v>2346.724861168232</v>
       </c>
       <c r="D42">
-        <v>2203.69548916367</v>
+        <v>2213.589091168232</v>
       </c>
       <c r="E42">
-        <v>1357.4182</v>
+        <v>1391.36123</v>
       </c>
       <c r="F42">
-        <v>1357.7212</v>
+        <v>1391.66423</v>
       </c>
       <c r="G42">
         <v>1524.8</v>
@@ -4859,28 +4859,28 @@
         <v>325.8</v>
       </c>
       <c r="M42">
-        <v>78.47628536000001</v>
+        <v>80.43819249400001</v>
       </c>
       <c r="N42">
-        <v>247.32371464</v>
+        <v>245.361807506</v>
       </c>
       <c r="O42">
-        <v>74.19711439199999</v>
+        <v>73.60854225179999</v>
       </c>
       <c r="P42">
-        <v>173.126600248</v>
+        <v>171.7532652542</v>
       </c>
       <c r="Q42">
-        <v>229.926600248</v>
+        <v>228.5532652542</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.144736254637146</v>
+        <v>0.1460701409669997</v>
       </c>
       <c r="T42">
-        <v>1.439643055130333</v>
+        <v>1.459052726520765</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.151572650329125</v>
+        <v>4.050314780808903</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1027699831705298</v>
+        <v>0.103543213558772</v>
       </c>
       <c r="C43">
-        <v>2346.724861168232</v>
+        <v>2283.140004070567</v>
       </c>
       <c r="D43">
-        <v>2213.589091168232</v>
+        <v>2183.947264070567</v>
       </c>
       <c r="E43">
-        <v>1391.36123</v>
+        <v>1425.30426</v>
       </c>
       <c r="F43">
-        <v>1391.66423</v>
+        <v>1425.60726</v>
       </c>
       <c r="G43">
         <v>1524.8</v>
@@ -4941,45 +4941,45 @@
         <v>325.8</v>
       </c>
       <c r="M43">
-        <v>80.43819249400001</v>
+        <v>87.38972503799999</v>
       </c>
       <c r="N43">
-        <v>245.361807506</v>
+        <v>238.410274962</v>
       </c>
       <c r="O43">
-        <v>73.60854225179999</v>
+        <v>71.5230824886</v>
       </c>
       <c r="P43">
-        <v>171.7532652542</v>
+        <v>166.8871924734</v>
       </c>
       <c r="Q43">
-        <v>228.5532652542</v>
+        <v>223.6871924734</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1460701409669997</v>
+        <v>0.1474500233771931</v>
       </c>
       <c r="T43">
-        <v>1.459052726520765</v>
+        <v>1.47913169692466</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.3</v>
       </c>
       <c r="W43">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.050314780808903</v>
+        <v>3.728127075103294</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.103543213558772</v>
+        <v>0.1033119439470142</v>
       </c>
       <c r="C44">
-        <v>2283.140004070567</v>
+        <v>2257.979160885994</v>
       </c>
       <c r="D44">
-        <v>2183.947264070566</v>
+        <v>2192.729450885994</v>
       </c>
       <c r="E44">
-        <v>1425.30426</v>
+        <v>1459.24729</v>
       </c>
       <c r="F44">
-        <v>1425.60726</v>
+        <v>1459.55029</v>
       </c>
       <c r="G44">
         <v>1524.8</v>
@@ -5023,28 +5023,28 @@
         <v>325.8</v>
       </c>
       <c r="M44">
-        <v>87.38972503799999</v>
+        <v>89.470432777</v>
       </c>
       <c r="N44">
-        <v>238.410274962</v>
+        <v>236.329567223</v>
       </c>
       <c r="O44">
-        <v>71.5230824886</v>
+        <v>70.89887016690001</v>
       </c>
       <c r="P44">
-        <v>166.8871924734</v>
+        <v>165.4306970561</v>
       </c>
       <c r="Q44">
-        <v>223.6871924734</v>
+        <v>222.2306970561</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1474500233771931</v>
+        <v>0.14887832271406</v>
       </c>
       <c r="T44">
-        <v>1.47913169692466</v>
+        <v>1.499915192605885</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.728127075103294</v>
+        <v>3.641426445449729</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1033119439470142</v>
+        <v>0.1030806743352564</v>
       </c>
       <c r="C45">
-        <v>2257.979160885994</v>
+        <v>2232.889233519323</v>
       </c>
       <c r="D45">
-        <v>2192.729450885994</v>
+        <v>2201.582553519323</v>
       </c>
       <c r="E45">
-        <v>1459.24729</v>
+        <v>1493.19032</v>
       </c>
       <c r="F45">
-        <v>1459.55029</v>
+        <v>1493.49332</v>
       </c>
       <c r="G45">
         <v>1524.8</v>
@@ -5105,28 +5105,28 @@
         <v>325.8</v>
       </c>
       <c r="M45">
-        <v>89.470432777</v>
+        <v>91.551140516</v>
       </c>
       <c r="N45">
-        <v>236.329567223</v>
+        <v>234.248859484</v>
       </c>
       <c r="O45">
-        <v>70.89887016690001</v>
+        <v>70.2746578452</v>
       </c>
       <c r="P45">
-        <v>165.4306970561</v>
+        <v>163.9742016388</v>
       </c>
       <c r="Q45">
-        <v>222.2306970561</v>
+        <v>220.7742016388</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.14887832271406</v>
+        <v>0.1503576327415293</v>
       </c>
       <c r="T45">
-        <v>1.499915192605885</v>
+        <v>1.52144095599001</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.641426445449729</v>
+        <v>3.558666753507689</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1030806743352564</v>
+        <v>0.1037314047234986</v>
       </c>
       <c r="C46">
-        <v>2232.889233519323</v>
+        <v>2174.216323816996</v>
       </c>
       <c r="D46">
-        <v>2201.582553519323</v>
+        <v>2176.852673816996</v>
       </c>
       <c r="E46">
-        <v>1493.19032</v>
+        <v>1527.13335</v>
       </c>
       <c r="F46">
-        <v>1493.49332</v>
+        <v>1527.43635</v>
       </c>
       <c r="G46">
         <v>1524.8</v>
@@ -5187,45 +5187,45 @@
         <v>325.8</v>
       </c>
       <c r="M46">
-        <v>91.551140516</v>
+        <v>97.908670035</v>
       </c>
       <c r="N46">
-        <v>234.248859484</v>
+        <v>227.891329965</v>
       </c>
       <c r="O46">
-        <v>70.2746578452</v>
+        <v>68.3673989895</v>
       </c>
       <c r="P46">
-        <v>163.9742016388</v>
+        <v>159.5239309755</v>
       </c>
       <c r="Q46">
-        <v>220.7742016388</v>
+        <v>216.3239309755</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1503576327415293</v>
+        <v>0.1518907358609066</v>
       </c>
       <c r="T46">
-        <v>1.52144095599001</v>
+        <v>1.543749474406286</v>
       </c>
       <c r="U46">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.558666753507689</v>
+        <v>3.327590905724021</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1037314047234986</v>
+        <v>0.1035197351117408</v>
       </c>
       <c r="C47">
-        <v>2174.216323816996</v>
+        <v>2148.256240367752</v>
       </c>
       <c r="D47">
-        <v>2176.852673816996</v>
+        <v>2184.835620367753</v>
       </c>
       <c r="E47">
-        <v>1527.13335</v>
+        <v>1561.07638</v>
       </c>
       <c r="F47">
-        <v>1527.43635</v>
+        <v>1561.37938</v>
       </c>
       <c r="G47">
         <v>1524.8</v>
@@ -5269,28 +5269,28 @@
         <v>325.8</v>
       </c>
       <c r="M47">
-        <v>97.908670035</v>
+        <v>100.084418258</v>
       </c>
       <c r="N47">
-        <v>227.891329965</v>
+        <v>225.715581742</v>
       </c>
       <c r="O47">
-        <v>68.3673989895</v>
+        <v>67.71467452259999</v>
       </c>
       <c r="P47">
-        <v>159.5239309755</v>
+        <v>158.0009072194</v>
       </c>
       <c r="Q47">
-        <v>216.3239309755</v>
+        <v>214.8009072194</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1518907358609066</v>
+        <v>0.1534806205772978</v>
       </c>
       <c r="T47">
-        <v>1.543749474406286</v>
+        <v>1.566884234245387</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.327590905724021</v>
+        <v>3.25525197299089</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1035197351117408</v>
+        <v>0.103308065499983</v>
       </c>
       <c r="C48">
-        <v>2148.256240367752</v>
+        <v>2122.354922491037</v>
       </c>
       <c r="D48">
-        <v>2184.835620367753</v>
+        <v>2192.877332491037</v>
       </c>
       <c r="E48">
-        <v>1561.07638</v>
+        <v>1595.01941</v>
       </c>
       <c r="F48">
-        <v>1561.37938</v>
+        <v>1595.32241</v>
       </c>
       <c r="G48">
         <v>1524.8</v>
@@ -5351,28 +5351,28 @@
         <v>325.8</v>
       </c>
       <c r="M48">
-        <v>100.084418258</v>
+        <v>102.260166481</v>
       </c>
       <c r="N48">
-        <v>225.715581742</v>
+        <v>223.539833519</v>
       </c>
       <c r="O48">
-        <v>67.71467452259999</v>
+        <v>67.0619500557</v>
       </c>
       <c r="P48">
-        <v>158.0009072194</v>
+        <v>156.4778834633</v>
       </c>
       <c r="Q48">
-        <v>214.8009072194</v>
+        <v>213.2778834633</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1534806205772978</v>
+        <v>0.1551305009433642</v>
       </c>
       <c r="T48">
-        <v>1.566884234245387</v>
+        <v>1.590892003889737</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.25525197299089</v>
+        <v>3.185991292714488</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.103308065499983</v>
+        <v>0.1030963958882252</v>
       </c>
       <c r="C49">
-        <v>2122.354922491037</v>
+        <v>2096.513021478388</v>
       </c>
       <c r="D49">
-        <v>2192.877332491037</v>
+        <v>2200.978461478388</v>
       </c>
       <c r="E49">
-        <v>1595.01941</v>
+        <v>1628.96244</v>
       </c>
       <c r="F49">
-        <v>1595.32241</v>
+        <v>1629.26544</v>
       </c>
       <c r="G49">
         <v>1524.8</v>
@@ -5433,28 +5433,28 @@
         <v>325.8</v>
       </c>
       <c r="M49">
-        <v>102.260166481</v>
+        <v>104.435914704</v>
       </c>
       <c r="N49">
-        <v>223.539833519</v>
+        <v>221.364085296</v>
       </c>
       <c r="O49">
-        <v>67.0619500557</v>
+        <v>66.4092255888</v>
       </c>
       <c r="P49">
-        <v>156.4778834633</v>
+        <v>154.9548597072</v>
       </c>
       <c r="Q49">
-        <v>213.2778834633</v>
+        <v>211.7548597072</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1551305009433642</v>
+        <v>0.1568438382465869</v>
       </c>
       <c r="T49">
-        <v>1.590892003889737</v>
+        <v>1.615823149289639</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.185991292714488</v>
+        <v>3.11961647411627</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1030963958882252</v>
+        <v>0.1028847262764674</v>
       </c>
       <c r="C50">
-        <v>2096.513021478388</v>
+        <v>2070.731198281274</v>
       </c>
       <c r="D50">
-        <v>2200.978461478388</v>
+        <v>2209.139668281274</v>
       </c>
       <c r="E50">
-        <v>1628.96244</v>
+        <v>1662.90547</v>
       </c>
       <c r="F50">
-        <v>1629.26544</v>
+        <v>1663.20847</v>
       </c>
       <c r="G50">
         <v>1524.8</v>
@@ -5515,28 +5515,28 @@
         <v>325.8</v>
       </c>
       <c r="M50">
-        <v>104.435914704</v>
+        <v>106.611662927</v>
       </c>
       <c r="N50">
-        <v>221.364085296</v>
+        <v>219.188337073</v>
       </c>
       <c r="O50">
-        <v>66.4092255888</v>
+        <v>65.7565011219</v>
       </c>
       <c r="P50">
-        <v>154.9548597072</v>
+        <v>153.4318359511</v>
       </c>
       <c r="Q50">
-        <v>211.7548597072</v>
+        <v>210.2318359511</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1568438382465869</v>
+        <v>0.1586243652479753</v>
       </c>
       <c r="T50">
-        <v>1.615823149289639</v>
+        <v>1.641731986666007</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.11961647411627</v>
+        <v>3.055950831787367</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1028847262764674</v>
+        <v>0.1054030566647096</v>
       </c>
       <c r="C51">
-        <v>2070.731198281274</v>
+        <v>1943.448264762566</v>
       </c>
       <c r="D51">
-        <v>2209.139668281274</v>
+        <v>2115.799764762567</v>
       </c>
       <c r="E51">
-        <v>1662.90547</v>
+        <v>1696.8485</v>
       </c>
       <c r="F51">
-        <v>1663.20847</v>
+        <v>1697.1515</v>
       </c>
       <c r="G51">
         <v>1524.8</v>
@@ -5597,45 +5597,45 @@
         <v>325.8</v>
       </c>
       <c r="M51">
-        <v>106.611662927</v>
+        <v>122.02519285</v>
       </c>
       <c r="N51">
-        <v>219.188337073</v>
+        <v>203.77480715</v>
       </c>
       <c r="O51">
-        <v>65.7565011219</v>
+        <v>61.132442145</v>
       </c>
       <c r="P51">
-        <v>153.4318359511</v>
+        <v>142.642365005</v>
       </c>
       <c r="Q51">
-        <v>210.2318359511</v>
+        <v>199.442365005</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1586243652479753</v>
+        <v>0.1604761133294192</v>
       </c>
       <c r="T51">
-        <v>1.641731986666007</v>
+        <v>1.668677177537431</v>
       </c>
       <c r="U51">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V51">
         <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.055950831787367</v>
+        <v>2.669940463855616</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1054030566647096</v>
+        <v>0.1052459870529518</v>
       </c>
       <c r="C52">
-        <v>1943.448264762566</v>
+        <v>1915.095651611268</v>
       </c>
       <c r="D52">
-        <v>2115.799764762567</v>
+        <v>2121.390181611268</v>
       </c>
       <c r="E52">
-        <v>1696.8485</v>
+        <v>1730.79153</v>
       </c>
       <c r="F52">
-        <v>1697.1515</v>
+        <v>1731.09453</v>
       </c>
       <c r="G52">
         <v>1524.8</v>
@@ -5679,28 +5679,28 @@
         <v>325.8</v>
       </c>
       <c r="M52">
-        <v>122.02519285</v>
+        <v>124.465696707</v>
       </c>
       <c r="N52">
-        <v>203.77480715</v>
+        <v>201.334303293</v>
       </c>
       <c r="O52">
-        <v>61.132442145</v>
+        <v>60.4002909879</v>
       </c>
       <c r="P52">
-        <v>142.642365005</v>
+        <v>140.9340123051</v>
       </c>
       <c r="Q52">
-        <v>199.442365005</v>
+        <v>197.7340123051</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1604761133294192</v>
+        <v>0.1624034429652078</v>
       </c>
       <c r="T52">
-        <v>1.668677177537431</v>
+        <v>1.696722172117892</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.669940463855616</v>
+        <v>2.617588690054525</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1052459870529518</v>
+        <v>0.105088917441194</v>
       </c>
       <c r="C53">
-        <v>1915.095651611268</v>
+        <v>1886.772658990816</v>
       </c>
       <c r="D53">
-        <v>2121.390181611268</v>
+        <v>2127.010218990816</v>
       </c>
       <c r="E53">
-        <v>1730.79153</v>
+        <v>1764.73456</v>
       </c>
       <c r="F53">
-        <v>1731.09453</v>
+        <v>1765.03756</v>
       </c>
       <c r="G53">
         <v>1524.8</v>
@@ -5761,28 +5761,28 @@
         <v>325.8</v>
       </c>
       <c r="M53">
-        <v>124.465696707</v>
+        <v>126.906200564</v>
       </c>
       <c r="N53">
-        <v>201.334303293</v>
+        <v>198.893799436</v>
       </c>
       <c r="O53">
-        <v>60.4002909879</v>
+        <v>59.66813983079999</v>
       </c>
       <c r="P53">
-        <v>140.9340123051</v>
+        <v>139.2256596052</v>
       </c>
       <c r="Q53">
-        <v>197.7340123051</v>
+        <v>196.0256596052</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1624034429652078</v>
+        <v>0.1644110780024876</v>
       </c>
       <c r="T53">
-        <v>1.696722172117892</v>
+        <v>1.725935708139205</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.617588690054525</v>
+        <v>2.567250446015016</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.105088917441194</v>
+        <v>0.1049318478294362</v>
       </c>
       <c r="C54">
-        <v>1886.772658990816</v>
+        <v>1858.479522940781</v>
       </c>
       <c r="D54">
-        <v>2127.010218990816</v>
+        <v>2132.660112940781</v>
       </c>
       <c r="E54">
-        <v>1764.73456</v>
+        <v>1798.67759</v>
       </c>
       <c r="F54">
-        <v>1765.03756</v>
+        <v>1798.98059</v>
       </c>
       <c r="G54">
         <v>1524.8</v>
@@ -5843,28 +5843,28 @@
         <v>325.8</v>
       </c>
       <c r="M54">
-        <v>126.906200564</v>
+        <v>129.346704421</v>
       </c>
       <c r="N54">
-        <v>198.893799436</v>
+        <v>196.453295579</v>
       </c>
       <c r="O54">
-        <v>59.66813983079999</v>
+        <v>58.9359886737</v>
       </c>
       <c r="P54">
-        <v>139.2256596052</v>
+        <v>137.5173069053</v>
       </c>
       <c r="Q54">
-        <v>196.0256596052</v>
+        <v>194.3173069053</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1644110780024876</v>
+        <v>0.1665041443179494</v>
       </c>
       <c r="T54">
-        <v>1.725935708139205</v>
+        <v>1.756392373352915</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.567250446015016</v>
+        <v>2.518811758354354</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1049318478294362</v>
+        <v>0.1062489782176784</v>
       </c>
       <c r="C55">
-        <v>1858.479522940781</v>
+        <v>1778.067693543856</v>
       </c>
       <c r="D55">
-        <v>2132.660112940781</v>
+        <v>2086.191313543857</v>
       </c>
       <c r="E55">
-        <v>1798.67759</v>
+        <v>1832.62062</v>
       </c>
       <c r="F55">
-        <v>1798.98059</v>
+        <v>1832.92362</v>
       </c>
       <c r="G55">
         <v>1524.8</v>
@@ -5925,45 +5925,45 @@
         <v>325.8</v>
       </c>
       <c r="M55">
-        <v>129.346704421</v>
+        <v>138.935610396</v>
       </c>
       <c r="N55">
-        <v>196.453295579</v>
+        <v>186.864389604</v>
       </c>
       <c r="O55">
-        <v>58.9359886737</v>
+        <v>56.0593168812</v>
       </c>
       <c r="P55">
-        <v>137.5173069053</v>
+        <v>130.8050727228</v>
       </c>
       <c r="Q55">
-        <v>194.3173069053</v>
+        <v>187.6050727228</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1665041443179494</v>
+        <v>0.1686882135166922</v>
       </c>
       <c r="T55">
-        <v>1.756392373352915</v>
+        <v>1.788173241402004</v>
       </c>
       <c r="U55">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
         <v>0.3</v>
       </c>
       <c r="W55">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.518811758354354</v>
+        <v>2.344971163774294</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1062489782176784</v>
+        <v>0.1061192086059206</v>
       </c>
       <c r="C56">
-        <v>1778.067693543856</v>
+        <v>1748.612856328012</v>
       </c>
       <c r="D56">
-        <v>2086.191313543857</v>
+        <v>2090.679506328013</v>
       </c>
       <c r="E56">
-        <v>1832.62062</v>
+        <v>1866.56365</v>
       </c>
       <c r="F56">
-        <v>1832.92362</v>
+        <v>1866.86665</v>
       </c>
       <c r="G56">
         <v>1524.8</v>
@@ -6007,28 +6007,28 @@
         <v>325.8</v>
       </c>
       <c r="M56">
-        <v>138.935610396</v>
+        <v>141.50849207</v>
       </c>
       <c r="N56">
-        <v>186.864389604</v>
+        <v>184.29150793</v>
       </c>
       <c r="O56">
-        <v>56.0593168812</v>
+        <v>55.28745237899999</v>
       </c>
       <c r="P56">
-        <v>130.8050727228</v>
+        <v>129.004055551</v>
       </c>
       <c r="Q56">
-        <v>187.6050727228</v>
+        <v>185.804055551</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1686882135166922</v>
+        <v>0.1709693524576014</v>
       </c>
       <c r="T56">
-        <v>1.788173241402004</v>
+        <v>1.821366592475496</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.344971163774294</v>
+        <v>2.302335324432943</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1061192086059206</v>
+        <v>0.1059894389941628</v>
       </c>
       <c r="C57">
-        <v>1748.612856328012</v>
+        <v>1719.177372375625</v>
       </c>
       <c r="D57">
-        <v>2090.679506328013</v>
+        <v>2095.187052375625</v>
       </c>
       <c r="E57">
-        <v>1866.56365</v>
+        <v>1900.50668</v>
       </c>
       <c r="F57">
-        <v>1866.86665</v>
+        <v>1900.80968</v>
       </c>
       <c r="G57">
         <v>1524.8</v>
@@ -6089,28 +6089,28 @@
         <v>325.8</v>
       </c>
       <c r="M57">
-        <v>141.50849207</v>
+        <v>144.081373744</v>
       </c>
       <c r="N57">
-        <v>184.29150793</v>
+        <v>181.718626256</v>
       </c>
       <c r="O57">
-        <v>55.28745237899999</v>
+        <v>54.5155878768</v>
       </c>
       <c r="P57">
-        <v>129.004055551</v>
+        <v>127.2030383792</v>
       </c>
       <c r="Q57">
-        <v>185.804055551</v>
+        <v>184.0030383792</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1709693524576014</v>
+        <v>0.1733541795321883</v>
       </c>
       <c r="T57">
-        <v>1.821366592475496</v>
+        <v>1.856068732234148</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.302335324432943</v>
+        <v>2.261222193639497</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1059894389941628</v>
+        <v>0.105859669382405</v>
       </c>
       <c r="C58">
-        <v>1719.177372375625</v>
+        <v>1689.761367135212</v>
       </c>
       <c r="D58">
-        <v>2095.187052375625</v>
+        <v>2099.714077135213</v>
       </c>
       <c r="E58">
-        <v>1900.50668</v>
+        <v>1934.44971</v>
       </c>
       <c r="F58">
-        <v>1900.80968</v>
+        <v>1934.75271</v>
       </c>
       <c r="G58">
         <v>1524.8</v>
@@ -6171,28 +6171,28 @@
         <v>325.8</v>
       </c>
       <c r="M58">
-        <v>144.081373744</v>
+        <v>146.654255418</v>
       </c>
       <c r="N58">
-        <v>181.718626256</v>
+        <v>179.145744582</v>
       </c>
       <c r="O58">
-        <v>54.5155878768</v>
+        <v>53.74372337459999</v>
       </c>
       <c r="P58">
-        <v>127.2030383792</v>
+        <v>125.4020212074</v>
       </c>
       <c r="Q58">
-        <v>184.0030383792</v>
+        <v>182.2020212074</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1733541795321883</v>
+        <v>0.1758499287962908</v>
       </c>
       <c r="T58">
-        <v>1.856068732234148</v>
+        <v>1.892384925004829</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.261222193639497</v>
+        <v>2.221551628838804</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.105859669382405</v>
+        <v>0.1057298997706472</v>
       </c>
       <c r="C59">
-        <v>1689.761367135212</v>
+        <v>1660.364967141853</v>
       </c>
       <c r="D59">
-        <v>2099.714077135213</v>
+        <v>2104.260707141853</v>
       </c>
       <c r="E59">
-        <v>1934.44971</v>
+        <v>1968.39274</v>
       </c>
       <c r="F59">
-        <v>1934.75271</v>
+        <v>1968.69574</v>
       </c>
       <c r="G59">
         <v>1524.8</v>
@@ -6253,28 +6253,28 @@
         <v>325.8</v>
       </c>
       <c r="M59">
-        <v>146.654255418</v>
+        <v>149.227137092</v>
       </c>
       <c r="N59">
-        <v>179.145744582</v>
+        <v>176.572862908</v>
       </c>
       <c r="O59">
-        <v>53.74372337459999</v>
+        <v>52.9718588724</v>
       </c>
       <c r="P59">
-        <v>125.4020212074</v>
+        <v>123.6010040356</v>
       </c>
       <c r="Q59">
-        <v>182.2020212074</v>
+        <v>180.4010040356</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1758499287962908</v>
+        <v>0.1784645232634458</v>
       </c>
       <c r="T59">
-        <v>1.892384925004829</v>
+        <v>1.930430460288401</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.221551628838804</v>
+        <v>2.18324901454848</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1057298997706472</v>
+        <v>0.1056001301588894</v>
       </c>
       <c r="C60">
-        <v>1660.364967141854</v>
+        <v>1630.988300028983</v>
       </c>
       <c r="D60">
-        <v>2104.260707141853</v>
+        <v>2108.827070028982</v>
       </c>
       <c r="E60">
-        <v>1968.39274</v>
+        <v>2002.33577</v>
       </c>
       <c r="F60">
-        <v>1968.69574</v>
+        <v>2002.63877</v>
       </c>
       <c r="G60">
         <v>1524.8</v>
@@ -6335,28 +6335,28 @@
         <v>325.8</v>
       </c>
       <c r="M60">
-        <v>149.227137092</v>
+        <v>151.800018766</v>
       </c>
       <c r="N60">
-        <v>176.572862908</v>
+        <v>173.999981234</v>
       </c>
       <c r="O60">
-        <v>52.97185887240001</v>
+        <v>52.1999943702</v>
       </c>
       <c r="P60">
-        <v>123.6010040356</v>
+        <v>121.7999868638</v>
       </c>
       <c r="Q60">
-        <v>180.4010040356</v>
+        <v>178.5999868638</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1784645232634458</v>
+        <v>0.1812066589241205</v>
       </c>
       <c r="T60">
-        <v>1.9304304602884</v>
+        <v>1.970331875341901</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.183249014548481</v>
+        <v>2.146244793962913</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1056001301588894</v>
+        <v>0.1054703605471316</v>
       </c>
       <c r="C61">
-        <v>1630.988300028983</v>
+        <v>1601.631494540326</v>
       </c>
       <c r="D61">
-        <v>2108.827070028982</v>
+        <v>2113.413294540326</v>
       </c>
       <c r="E61">
-        <v>2002.33577</v>
+        <v>2036.2788</v>
       </c>
       <c r="F61">
-        <v>2002.63877</v>
+        <v>2036.5818</v>
       </c>
       <c r="G61">
         <v>1524.8</v>
@@ -6417,28 +6417,28 @@
         <v>325.8</v>
       </c>
       <c r="M61">
-        <v>151.800018766</v>
+        <v>154.37290044</v>
       </c>
       <c r="N61">
-        <v>173.999981234</v>
+        <v>171.42709956</v>
       </c>
       <c r="O61">
-        <v>52.1999943702</v>
+        <v>51.42812986800001</v>
       </c>
       <c r="P61">
-        <v>121.7999868638</v>
+        <v>119.998969692</v>
       </c>
       <c r="Q61">
-        <v>178.5999868638</v>
+        <v>176.798969692</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1812066589241205</v>
+        <v>0.184085901367829</v>
       </c>
       <c r="T61">
-        <v>1.970331875341901</v>
+        <v>2.012228361148078</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.146244793962913</v>
+        <v>2.110474047396865</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1054703605471316</v>
+        <v>0.1053405909353738</v>
       </c>
       <c r="C62">
-        <v>1601.631494540326</v>
+        <v>1572.294680542011</v>
       </c>
       <c r="D62">
-        <v>2113.413294540326</v>
+        <v>2118.019510542011</v>
       </c>
       <c r="E62">
-        <v>2036.2788</v>
+        <v>2070.22183</v>
       </c>
       <c r="F62">
-        <v>2036.5818</v>
+        <v>2070.52483</v>
       </c>
       <c r="G62">
         <v>1524.8</v>
@@ -6499,28 +6499,28 @@
         <v>325.8</v>
       </c>
       <c r="M62">
-        <v>154.37290044</v>
+        <v>156.945782114</v>
       </c>
       <c r="N62">
-        <v>171.42709956</v>
+        <v>168.854217886</v>
       </c>
       <c r="O62">
-        <v>51.42812986800001</v>
+        <v>50.6562653658</v>
       </c>
       <c r="P62">
-        <v>119.998969692</v>
+        <v>118.1979525202</v>
       </c>
       <c r="Q62">
-        <v>176.798969692</v>
+        <v>174.9979525202</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.184085901367829</v>
+        <v>0.1871127972701893</v>
       </c>
       <c r="T62">
-        <v>2.012228361148078</v>
+        <v>2.056273384687905</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.110474047396865</v>
+        <v>2.075876112193638</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1053405909353738</v>
+        <v>0.105210821323616</v>
       </c>
       <c r="C63">
-        <v>1572.294680542011</v>
+        <v>1542.977989034814</v>
       </c>
       <c r="D63">
-        <v>2118.019510542011</v>
+        <v>2122.645849034813</v>
       </c>
       <c r="E63">
-        <v>2070.22183</v>
+        <v>2104.16486</v>
       </c>
       <c r="F63">
-        <v>2070.52483</v>
+        <v>2104.46786</v>
       </c>
       <c r="G63">
         <v>1524.8</v>
@@ -6581,28 +6581,28 @@
         <v>325.8</v>
       </c>
       <c r="M63">
-        <v>156.945782114</v>
+        <v>159.518663788</v>
       </c>
       <c r="N63">
-        <v>168.854217886</v>
+        <v>166.281336212</v>
       </c>
       <c r="O63">
-        <v>50.6562653658</v>
+        <v>49.8844008636</v>
       </c>
       <c r="P63">
-        <v>118.1979525202</v>
+        <v>116.3969353484</v>
       </c>
       <c r="Q63">
-        <v>174.9979525202</v>
+        <v>173.1969353484</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1871127972701893</v>
+        <v>0.1902990034832001</v>
       </c>
       <c r="T63">
-        <v>2.056273384687905</v>
+        <v>2.102636567361407</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.075876112193638</v>
+        <v>2.04239423941632</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.105210821323616</v>
+        <v>0.1050810517118582</v>
       </c>
       <c r="C64">
-        <v>1542.977989034814</v>
+        <v>1513.681552166585</v>
       </c>
       <c r="D64">
-        <v>2122.645849034813</v>
+        <v>2127.292442166585</v>
       </c>
       <c r="E64">
-        <v>2104.16486</v>
+        <v>2138.10789</v>
       </c>
       <c r="F64">
-        <v>2104.46786</v>
+        <v>2138.41089</v>
       </c>
       <c r="G64">
         <v>1524.8</v>
@@ -6663,28 +6663,28 @@
         <v>325.8</v>
       </c>
       <c r="M64">
-        <v>159.518663788</v>
+        <v>162.091545462</v>
       </c>
       <c r="N64">
-        <v>166.281336212</v>
+        <v>163.708454538</v>
       </c>
       <c r="O64">
-        <v>49.8844008636</v>
+        <v>49.1125363614</v>
       </c>
       <c r="P64">
-        <v>116.3969353484</v>
+        <v>114.5959181766</v>
       </c>
       <c r="Q64">
-        <v>173.1969353484</v>
+        <v>171.3959181766</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1902990034832001</v>
+        <v>0.1936574370590763</v>
       </c>
       <c r="T64">
-        <v>2.102636567361407</v>
+        <v>2.15150586801726</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.04239423941632</v>
+        <v>2.009975283235109</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1050810517118582</v>
+        <v>0.1113128821001004</v>
       </c>
       <c r="C65">
-        <v>1513.681552166585</v>
+        <v>1277.382508191872</v>
       </c>
       <c r="D65">
-        <v>2127.292442166585</v>
+        <v>1924.936428191872</v>
       </c>
       <c r="E65">
-        <v>2138.10789</v>
+        <v>2172.05092</v>
       </c>
       <c r="F65">
-        <v>2138.41089</v>
+        <v>2172.35392</v>
       </c>
       <c r="G65">
         <v>1524.8</v>
@@ -6745,45 +6745,45 @@
         <v>325.8</v>
       </c>
       <c r="M65">
-        <v>162.091545462</v>
+        <v>195.5118528</v>
       </c>
       <c r="N65">
-        <v>163.708454538</v>
+        <v>130.2881472</v>
       </c>
       <c r="O65">
-        <v>49.1125363614</v>
+        <v>39.08644416000001</v>
       </c>
       <c r="P65">
-        <v>114.5959181766</v>
+        <v>91.20170304000001</v>
       </c>
       <c r="Q65">
-        <v>171.3959181766</v>
+        <v>148.00170304</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1936574370590763</v>
+        <v>0.1972024502780568</v>
       </c>
       <c r="T65">
-        <v>2.15150586801726</v>
+        <v>2.20309012982066</v>
       </c>
       <c r="U65">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V65">
         <v>0.3</v>
       </c>
       <c r="W65">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.009975283235109</v>
+        <v>1.666395133257108</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1113128821001004</v>
+        <v>0.1112825124883426</v>
       </c>
       <c r="C66">
-        <v>1277.382508191872</v>
+        <v>1244.332229092245</v>
       </c>
       <c r="D66">
-        <v>1924.936428191872</v>
+        <v>1925.829179092245</v>
       </c>
       <c r="E66">
-        <v>2172.05092</v>
+        <v>2205.99395</v>
       </c>
       <c r="F66">
-        <v>2172.35392</v>
+        <v>2206.29695</v>
       </c>
       <c r="G66">
         <v>1524.8</v>
@@ -6827,28 +6827,28 @@
         <v>325.8</v>
       </c>
       <c r="M66">
-        <v>195.5118528</v>
+        <v>198.5667255</v>
       </c>
       <c r="N66">
-        <v>130.2881472</v>
+        <v>127.2332745</v>
       </c>
       <c r="O66">
-        <v>39.08644416000001</v>
+        <v>38.16998235000001</v>
       </c>
       <c r="P66">
-        <v>91.20170304000001</v>
+        <v>89.06329215000002</v>
       </c>
       <c r="Q66">
-        <v>148.00170304</v>
+        <v>145.86329215</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1972024502780568</v>
+        <v>0.2009500356809789</v>
       </c>
       <c r="T66">
-        <v>2.20309012982066</v>
+        <v>2.257622063727112</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.666395133257108</v>
+        <v>1.640758285053152</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1112825124883426</v>
+        <v>0.1112521428765848</v>
       </c>
       <c r="C67">
-        <v>1244.332229092245</v>
+        <v>1211.282778460473</v>
       </c>
       <c r="D67">
-        <v>1925.829179092245</v>
+        <v>1926.722758460473</v>
       </c>
       <c r="E67">
-        <v>2205.99395</v>
+        <v>2239.93698</v>
       </c>
       <c r="F67">
-        <v>2206.29695</v>
+        <v>2240.23998</v>
       </c>
       <c r="G67">
         <v>1524.8</v>
@@ -6909,28 +6909,28 @@
         <v>325.8</v>
       </c>
       <c r="M67">
-        <v>198.5667255</v>
+        <v>201.6215982</v>
       </c>
       <c r="N67">
-        <v>127.2332745</v>
+        <v>124.1784018</v>
       </c>
       <c r="O67">
-        <v>38.16998235000001</v>
+        <v>37.25352054000001</v>
       </c>
       <c r="P67">
-        <v>89.06329215000002</v>
+        <v>86.92488126000003</v>
       </c>
       <c r="Q67">
-        <v>145.86329215</v>
+        <v>143.72488126</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2009500356809789</v>
+        <v>0.2049180672840731</v>
       </c>
       <c r="T67">
-        <v>2.257622063727112</v>
+        <v>2.315361758451591</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.640758285053152</v>
+        <v>1.615898311037196</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1112521428765848</v>
+        <v>0.111221773264827</v>
       </c>
       <c r="C68">
-        <v>1211.282778460473</v>
+        <v>1178.234157450313</v>
       </c>
       <c r="D68">
-        <v>1926.722758460473</v>
+        <v>1927.617167450313</v>
       </c>
       <c r="E68">
-        <v>2239.93698</v>
+        <v>2273.88001</v>
       </c>
       <c r="F68">
-        <v>2240.23998</v>
+        <v>2274.18301</v>
       </c>
       <c r="G68">
         <v>1524.8</v>
@@ -6991,28 +6991,28 @@
         <v>325.8</v>
       </c>
       <c r="M68">
-        <v>201.6215982</v>
+        <v>204.6764709</v>
       </c>
       <c r="N68">
-        <v>124.1784018</v>
+        <v>121.1235291</v>
       </c>
       <c r="O68">
-        <v>37.25352054000001</v>
+        <v>36.33705873</v>
       </c>
       <c r="P68">
-        <v>86.92488126000003</v>
+        <v>84.78647037000002</v>
       </c>
       <c r="Q68">
-        <v>143.72488126</v>
+        <v>141.58647037</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2049180672840731</v>
+        <v>0.209126585650991</v>
       </c>
       <c r="T68">
-        <v>2.315361758451591</v>
+        <v>2.376600828613917</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.615898311037196</v>
+        <v>1.591780425797834</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.111221773264827</v>
+        <v>0.1111914036530692</v>
       </c>
       <c r="C69">
-        <v>1178.234157450313</v>
+        <v>1145.186367217664</v>
       </c>
       <c r="D69">
-        <v>1927.617167450313</v>
+        <v>1928.512407217665</v>
       </c>
       <c r="E69">
-        <v>2273.88001</v>
+        <v>2307.82304</v>
       </c>
       <c r="F69">
-        <v>2274.18301</v>
+        <v>2308.12604</v>
       </c>
       <c r="G69">
         <v>1524.8</v>
@@ -7073,28 +7073,28 @@
         <v>325.8</v>
       </c>
       <c r="M69">
-        <v>204.6764709</v>
+        <v>207.7313436</v>
       </c>
       <c r="N69">
-        <v>121.1235291</v>
+        <v>118.0686564</v>
       </c>
       <c r="O69">
-        <v>36.33705873</v>
+        <v>35.42059692</v>
       </c>
       <c r="P69">
-        <v>84.78647037000002</v>
+        <v>82.64805948</v>
       </c>
       <c r="Q69">
-        <v>141.58647037</v>
+        <v>139.44805948</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.209126585650991</v>
+        <v>0.2135981364158414</v>
       </c>
       <c r="T69">
-        <v>2.376600828613917</v>
+        <v>2.441667340661388</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.591780425797834</v>
+        <v>1.568371890124336</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1111914036530692</v>
+        <v>0.1111610340413114</v>
       </c>
       <c r="C70">
-        <v>1145.186367217664</v>
+        <v>1112.139408920574</v>
       </c>
       <c r="D70">
-        <v>1928.512407217665</v>
+        <v>1929.408478920574</v>
       </c>
       <c r="E70">
-        <v>2307.82304</v>
+        <v>2341.76607</v>
       </c>
       <c r="F70">
-        <v>2308.12604</v>
+        <v>2342.06907</v>
       </c>
       <c r="G70">
         <v>1524.8</v>
@@ -7155,28 +7155,28 @@
         <v>325.8</v>
       </c>
       <c r="M70">
-        <v>207.7313436</v>
+        <v>210.7862163</v>
       </c>
       <c r="N70">
-        <v>118.0686564</v>
+        <v>115.0137837</v>
       </c>
       <c r="O70">
-        <v>35.42059692</v>
+        <v>34.50413511</v>
       </c>
       <c r="P70">
-        <v>82.64805948</v>
+        <v>80.50964859000001</v>
       </c>
       <c r="Q70">
-        <v>139.44805948</v>
+        <v>137.30964859</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2135981364158414</v>
+        <v>0.2183581743268111</v>
       </c>
       <c r="T70">
-        <v>2.441667340661388</v>
+        <v>2.510931692195793</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.568371890124336</v>
+        <v>1.54564186273123</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1111610340413114</v>
+        <v>0.1111306644295537</v>
       </c>
       <c r="C71">
-        <v>1112.139408920574</v>
+        <v>1079.093283719241</v>
       </c>
       <c r="D71">
-        <v>1929.408478920574</v>
+        <v>1930.305383719241</v>
       </c>
       <c r="E71">
-        <v>2341.76607</v>
+        <v>2375.7091</v>
       </c>
       <c r="F71">
-        <v>2342.06907</v>
+        <v>2376.0121</v>
       </c>
       <c r="G71">
         <v>1524.8</v>
@@ -7237,28 +7237,28 @@
         <v>325.8</v>
       </c>
       <c r="M71">
-        <v>210.7862163</v>
+        <v>213.841089</v>
       </c>
       <c r="N71">
-        <v>115.0137837</v>
+        <v>111.958911</v>
       </c>
       <c r="O71">
-        <v>34.50413511</v>
+        <v>33.58767330000001</v>
       </c>
       <c r="P71">
-        <v>80.50964859000001</v>
+        <v>78.37123770000002</v>
       </c>
       <c r="Q71">
-        <v>137.30964859</v>
+        <v>135.1712377</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2183581743268111</v>
+        <v>0.2234355480985122</v>
       </c>
       <c r="T71">
-        <v>2.510931692195793</v>
+        <v>2.584813667165825</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.54564186273123</v>
+        <v>1.523561264692213</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1111306644295537</v>
+        <v>0.1111002948177959</v>
       </c>
       <c r="C72">
-        <v>1079.093283719241</v>
+        <v>1046.047992776026</v>
       </c>
       <c r="D72">
-        <v>1930.305383719241</v>
+        <v>1931.203122776026</v>
       </c>
       <c r="E72">
-        <v>2375.7091</v>
+        <v>2409.65213</v>
       </c>
       <c r="F72">
-        <v>2376.0121</v>
+        <v>2409.95513</v>
       </c>
       <c r="G72">
         <v>1524.8</v>
@@ -7319,28 +7319,28 @@
         <v>325.8</v>
       </c>
       <c r="M72">
-        <v>213.841089</v>
+        <v>216.8959617</v>
       </c>
       <c r="N72">
-        <v>111.958911</v>
+        <v>108.9040383</v>
       </c>
       <c r="O72">
-        <v>33.58767330000001</v>
+        <v>32.67121149</v>
       </c>
       <c r="P72">
-        <v>78.37123770000002</v>
+        <v>76.23282681000001</v>
       </c>
       <c r="Q72">
-        <v>135.1712377</v>
+        <v>133.03282681</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2234355480985122</v>
+        <v>0.2288630855786064</v>
       </c>
       <c r="T72">
-        <v>2.584813667165825</v>
+        <v>2.66379095075448</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.523561264692213</v>
+        <v>1.50210265533035</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1111002948177958</v>
+        <v>0.143949405370098</v>
       </c>
       <c r="C73">
-        <v>1046.047992776027</v>
+        <v>365.7607018015451</v>
       </c>
       <c r="D73">
-        <v>1931.203122776027</v>
+        <v>1284.858861801545</v>
       </c>
       <c r="E73">
-        <v>2409.65213</v>
+        <v>2443.59516</v>
       </c>
       <c r="F73">
-        <v>2409.95513</v>
+        <v>2443.89816</v>
       </c>
       <c r="G73">
         <v>1524.8</v>
@@ -7401,45 +7401,45 @@
         <v>325.8</v>
       </c>
       <c r="M73">
-        <v>216.8959617</v>
+        <v>358.764249888</v>
       </c>
       <c r="N73">
-        <v>108.9040383</v>
+        <v>-32.96424988799998</v>
       </c>
       <c r="O73">
-        <v>32.67121149</v>
+        <v>-9.889274966399995</v>
       </c>
       <c r="P73">
-        <v>76.23282681000002</v>
+        <v>-23.07497492159999</v>
       </c>
       <c r="Q73">
-        <v>133.03282681</v>
+        <v>33.72502507840002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2288630855786064</v>
+        <v>0.2394596902599313</v>
       </c>
       <c r="T73">
-        <v>2.663790950754479</v>
+        <v>2.817984460437868</v>
       </c>
       <c r="U73">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.3</v>
+        <v>0.2724351716496634</v>
       </c>
       <c r="W73">
-        <v>0.063</v>
+        <v>0.1068065168018294</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.502102655330351</v>
+        <v>0.9081172388322113</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.143949405370098</v>
+        <v>0.1449594053700979</v>
       </c>
       <c r="C74">
-        <v>365.7607018015451</v>
+        <v>318.7305879734809</v>
       </c>
       <c r="D74">
-        <v>1284.858861801545</v>
+        <v>1271.771777973481</v>
       </c>
       <c r="E74">
-        <v>2443.59516</v>
+        <v>2477.53819</v>
       </c>
       <c r="F74">
-        <v>2443.89816</v>
+        <v>2477.84119</v>
       </c>
       <c r="G74">
         <v>1524.8</v>
@@ -7483,37 +7483,37 @@
         <v>325.8</v>
       </c>
       <c r="M74">
-        <v>358.764249888</v>
+        <v>363.747086692</v>
       </c>
       <c r="N74">
-        <v>-32.96424988799998</v>
+        <v>-37.94708669199997</v>
       </c>
       <c r="O74">
-        <v>-9.889274966399995</v>
+        <v>-11.38412600759999</v>
       </c>
       <c r="P74">
-        <v>-23.07497492159999</v>
+        <v>-26.56296068439998</v>
       </c>
       <c r="Q74">
-        <v>33.72502507840002</v>
+        <v>30.23703931560003</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2394596902599313</v>
+        <v>0.2466322713806695</v>
       </c>
       <c r="T74">
-        <v>2.817984460437868</v>
+        <v>2.9223542552689</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2724351716496634</v>
+        <v>0.2687031829969282</v>
       </c>
       <c r="W74">
-        <v>0.1068065168018294</v>
+        <v>0.1073543727360509</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9081172388322113</v>
+        <v>0.8956772766564276</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1449594053700979</v>
+        <v>0.1459694053700979</v>
       </c>
       <c r="C75">
-        <v>318.7305879734809</v>
+        <v>271.964386157621</v>
       </c>
       <c r="D75">
-        <v>1271.771777973481</v>
+        <v>1258.948606157621</v>
       </c>
       <c r="E75">
-        <v>2477.53819</v>
+        <v>2511.48122</v>
       </c>
       <c r="F75">
-        <v>2477.84119</v>
+        <v>2511.78422</v>
       </c>
       <c r="G75">
         <v>1524.8</v>
@@ -7565,37 +7565,37 @@
         <v>325.8</v>
       </c>
       <c r="M75">
-        <v>363.747086692</v>
+        <v>368.729923496</v>
       </c>
       <c r="N75">
-        <v>-37.94708669199997</v>
+        <v>-42.92992349600001</v>
       </c>
       <c r="O75">
-        <v>-11.38412600759999</v>
+        <v>-12.8789770488</v>
       </c>
       <c r="P75">
-        <v>-26.56296068439998</v>
+        <v>-30.05094644720001</v>
       </c>
       <c r="Q75">
-        <v>30.23703931560003</v>
+        <v>26.7490535528</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2466322713806695</v>
+        <v>0.2543565895106952</v>
       </c>
       <c r="T75">
-        <v>2.9223542552689</v>
+        <v>3.034752495856165</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2687031829969282</v>
+        <v>0.2650720589023751</v>
       </c>
       <c r="W75">
-        <v>0.1073543727360509</v>
+        <v>0.1078874217531313</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8956772766564276</v>
+        <v>0.8835735296745838</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1459694053700979</v>
+        <v>0.146979405370098</v>
       </c>
       <c r="C76">
-        <v>271.964386157621</v>
+        <v>225.4541930321993</v>
       </c>
       <c r="D76">
-        <v>1258.948606157621</v>
+        <v>1246.381443032199</v>
       </c>
       <c r="E76">
-        <v>2511.48122</v>
+        <v>2545.42425</v>
       </c>
       <c r="F76">
-        <v>2511.78422</v>
+        <v>2545.72725</v>
       </c>
       <c r="G76">
         <v>1524.8</v>
@@ -7647,37 +7647,37 @@
         <v>325.8</v>
       </c>
       <c r="M76">
-        <v>368.729923496</v>
+        <v>373.7127603</v>
       </c>
       <c r="N76">
-        <v>-42.92992349600001</v>
+        <v>-47.9127603</v>
       </c>
       <c r="O76">
-        <v>-12.8789770488</v>
+        <v>-14.37382809</v>
       </c>
       <c r="P76">
-        <v>-30.05094644720001</v>
+        <v>-33.53893221</v>
       </c>
       <c r="Q76">
-        <v>26.7490535528</v>
+        <v>23.26106779000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2543565895106952</v>
+        <v>0.2626988530911231</v>
       </c>
       <c r="T76">
-        <v>3.034752495856165</v>
+        <v>3.156142595690412</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2650720589023751</v>
+        <v>0.2615377647836769</v>
       </c>
       <c r="W76">
-        <v>0.1078874217531313</v>
+        <v>0.1084062561297563</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8835735296745838</v>
+        <v>0.8717925492789228</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.146979405370098</v>
+        <v>0.147989405370098</v>
       </c>
       <c r="C77">
-        <v>225.4541930321993</v>
+        <v>179.192417728776</v>
       </c>
       <c r="D77">
-        <v>1246.381443032199</v>
+        <v>1234.062697728776</v>
       </c>
       <c r="E77">
-        <v>2545.42425</v>
+        <v>2579.36728</v>
       </c>
       <c r="F77">
-        <v>2545.72725</v>
+        <v>2579.67028</v>
       </c>
       <c r="G77">
         <v>1524.8</v>
@@ -7729,37 +7729,37 @@
         <v>325.8</v>
       </c>
       <c r="M77">
-        <v>373.7127603</v>
+        <v>378.695597104</v>
       </c>
       <c r="N77">
-        <v>-47.9127603</v>
+        <v>-52.89559710399999</v>
       </c>
       <c r="O77">
-        <v>-14.37382809</v>
+        <v>-15.8686791312</v>
       </c>
       <c r="P77">
-        <v>-33.53893221</v>
+        <v>-37.02691797279999</v>
       </c>
       <c r="Q77">
-        <v>23.26106779000001</v>
+        <v>19.77308202720002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2626988530911231</v>
+        <v>0.2717363053032532</v>
       </c>
       <c r="T77">
-        <v>3.156142595690412</v>
+        <v>3.287648537177513</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2615377647836769</v>
+        <v>0.2580964784049443</v>
       </c>
       <c r="W77">
-        <v>0.1084062561297563</v>
+        <v>0.1089114369701542</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8717925492789228</v>
+        <v>0.8603215946831475</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.147989405370098</v>
+        <v>0.148999405370098</v>
       </c>
       <c r="C78">
-        <v>179.192417728776</v>
+        <v>133.1717665425281</v>
       </c>
       <c r="D78">
-        <v>1234.062697728776</v>
+        <v>1221.985076542528</v>
       </c>
       <c r="E78">
-        <v>2579.36728</v>
+        <v>2613.31031</v>
       </c>
       <c r="F78">
-        <v>2579.67028</v>
+        <v>2613.61331</v>
       </c>
       <c r="G78">
         <v>1524.8</v>
@@ -7811,37 +7811,37 @@
         <v>325.8</v>
       </c>
       <c r="M78">
-        <v>378.695597104</v>
+        <v>383.678433908</v>
       </c>
       <c r="N78">
-        <v>-52.89559710399999</v>
+        <v>-57.87843390800003</v>
       </c>
       <c r="O78">
-        <v>-15.8686791312</v>
+        <v>-17.36353017240001</v>
       </c>
       <c r="P78">
-        <v>-37.02691797279999</v>
+        <v>-40.51490373560003</v>
       </c>
       <c r="Q78">
-        <v>19.77308202720002</v>
+        <v>16.28509626439998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2717363053032532</v>
+        <v>0.2815596229251338</v>
       </c>
       <c r="T78">
-        <v>3.287648537177513</v>
+        <v>3.430589777924361</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2580964784049443</v>
+        <v>0.2547445760879969</v>
       </c>
       <c r="W78">
-        <v>0.1089114369701542</v>
+        <v>0.1094034962302821</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8603215946831475</v>
+        <v>0.8491485869599896</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.148999405370098</v>
+        <v>0.1500094053700979</v>
       </c>
       <c r="C79">
-        <v>133.1717665425281</v>
+        <v>87.38522853166569</v>
       </c>
       <c r="D79">
-        <v>1221.985076542528</v>
+        <v>1210.141568531666</v>
       </c>
       <c r="E79">
-        <v>2613.31031</v>
+        <v>2647.25334</v>
       </c>
       <c r="F79">
-        <v>2613.61331</v>
+        <v>2647.55634</v>
       </c>
       <c r="G79">
         <v>1524.8</v>
@@ -7893,37 +7893,37 @@
         <v>325.8</v>
       </c>
       <c r="M79">
-        <v>383.678433908</v>
+        <v>388.661270712</v>
       </c>
       <c r="N79">
-        <v>-57.87843390800003</v>
+        <v>-62.86127071200002</v>
       </c>
       <c r="O79">
-        <v>-17.36353017240001</v>
+        <v>-18.8583812136</v>
       </c>
       <c r="P79">
-        <v>-40.51490373560003</v>
+        <v>-44.00288949840002</v>
       </c>
       <c r="Q79">
-        <v>16.28509626439998</v>
+        <v>12.7971105016</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2815596229251338</v>
+        <v>0.2922759694217307</v>
       </c>
       <c r="T79">
-        <v>3.430589777924361</v>
+        <v>3.586525676920923</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2547445760879969</v>
+        <v>0.2514786199843046</v>
       </c>
       <c r="W79">
-        <v>0.1094034962302821</v>
+        <v>0.1098829385863041</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8491485869599896</v>
+        <v>0.8382620666143488</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1500094053700979</v>
+        <v>0.1510194053700979</v>
       </c>
       <c r="C80">
-        <v>87.38522853166569</v>
+        <v>41.82606194623395</v>
       </c>
       <c r="D80">
-        <v>1210.141568531666</v>
+        <v>1198.525431946234</v>
       </c>
       <c r="E80">
-        <v>2647.25334</v>
+        <v>2681.19637</v>
       </c>
       <c r="F80">
-        <v>2647.55634</v>
+        <v>2681.49937</v>
       </c>
       <c r="G80">
         <v>1524.8</v>
@@ -7975,37 +7975,37 @@
         <v>325.8</v>
       </c>
       <c r="M80">
-        <v>388.661270712</v>
+        <v>393.644107516</v>
       </c>
       <c r="N80">
-        <v>-62.86127071200002</v>
+        <v>-67.84410751600001</v>
       </c>
       <c r="O80">
-        <v>-18.8583812136</v>
+        <v>-20.3532322548</v>
       </c>
       <c r="P80">
-        <v>-44.00288949840002</v>
+        <v>-47.4908752612</v>
       </c>
       <c r="Q80">
-        <v>12.7971105016</v>
+        <v>9.309124738800008</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2922759694217307</v>
+        <v>0.3040129203465751</v>
       </c>
       <c r="T80">
-        <v>3.586525676920923</v>
+        <v>3.757312613917158</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2514786199843046</v>
+        <v>0.2482953463136172</v>
       </c>
       <c r="W80">
-        <v>0.1098829385863041</v>
+        <v>0.110350243161161</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8382620666143488</v>
+        <v>0.8276511543787242</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1510194053700979</v>
+        <v>0.152029405370098</v>
       </c>
       <c r="C81">
-        <v>41.82606194623395</v>
+        <v>-3.512218568896969</v>
       </c>
       <c r="D81">
-        <v>1198.525431946234</v>
+        <v>1187.130181431103</v>
       </c>
       <c r="E81">
-        <v>2681.19637</v>
+        <v>2715.1394</v>
       </c>
       <c r="F81">
-        <v>2681.49937</v>
+        <v>2715.4424</v>
       </c>
       <c r="G81">
         <v>1524.8</v>
@@ -8057,37 +8057,37 @@
         <v>325.8</v>
       </c>
       <c r="M81">
-        <v>393.644107516</v>
+        <v>398.62694432</v>
       </c>
       <c r="N81">
-        <v>-67.84410751600001</v>
+        <v>-72.82694432</v>
       </c>
       <c r="O81">
-        <v>-20.3532322548</v>
+        <v>-21.848083296</v>
       </c>
       <c r="P81">
-        <v>-47.4908752612</v>
+        <v>-50.978861024</v>
       </c>
       <c r="Q81">
-        <v>9.309124738800008</v>
+        <v>5.821138976000015</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3040129203465751</v>
+        <v>0.3169235663639039</v>
       </c>
       <c r="T81">
-        <v>3.757312613917158</v>
+        <v>3.945178244613016</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2482953463136172</v>
+        <v>0.245191654484697</v>
       </c>
       <c r="W81">
-        <v>0.110350243161161</v>
+        <v>0.1108058651216465</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8276511543787242</v>
+        <v>0.8173055149489901</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.152029405370098</v>
+        <v>0.153039405370098</v>
       </c>
       <c r="C82">
-        <v>-3.512218568896969</v>
+        <v>-48.63585404789592</v>
       </c>
       <c r="D82">
-        <v>1187.130181431103</v>
+        <v>1175.949575952104</v>
       </c>
       <c r="E82">
-        <v>2715.1394</v>
+        <v>2749.08243</v>
       </c>
       <c r="F82">
-        <v>2715.4424</v>
+        <v>2749.38543</v>
       </c>
       <c r="G82">
         <v>1524.8</v>
@@ -8139,37 +8139,37 @@
         <v>325.8</v>
       </c>
       <c r="M82">
-        <v>398.62694432</v>
+        <v>403.6097811240001</v>
       </c>
       <c r="N82">
-        <v>-72.82694432</v>
+        <v>-77.80978112400004</v>
       </c>
       <c r="O82">
-        <v>-21.848083296</v>
+        <v>-23.34293433720001</v>
       </c>
       <c r="P82">
-        <v>-50.978861024</v>
+        <v>-54.46684678680003</v>
       </c>
       <c r="Q82">
-        <v>5.821138976000015</v>
+        <v>2.333153213199978</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3169235663639039</v>
+        <v>0.3311932277514777</v>
       </c>
       <c r="T82">
-        <v>3.945178244613016</v>
+        <v>4.152819204855806</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.245191654484697</v>
+        <v>0.2421645970219229</v>
       </c>
       <c r="W82">
-        <v>0.1108058651216465</v>
+        <v>0.1112502371571817</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8173055149489901</v>
+        <v>0.8072153234064099</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.153039405370098</v>
+        <v>0.2018877644084955</v>
       </c>
       <c r="C83">
-        <v>-48.63585404789592</v>
+        <v>-450.5975260910077</v>
       </c>
       <c r="D83">
-        <v>1175.949575952104</v>
+        <v>807.9309339089924</v>
       </c>
       <c r="E83">
-        <v>2749.08243</v>
+        <v>2783.02546</v>
       </c>
       <c r="F83">
-        <v>2749.38543</v>
+        <v>2783.32846</v>
       </c>
       <c r="G83">
         <v>1524.8</v>
@@ -8221,45 +8221,45 @@
         <v>325.8</v>
       </c>
       <c r="M83">
-        <v>403.6097811240001</v>
+        <v>558.892354768</v>
       </c>
       <c r="N83">
-        <v>-77.80978112400004</v>
+        <v>-233.092354768</v>
       </c>
       <c r="O83">
-        <v>-23.34293433720001</v>
+        <v>-69.92770643039999</v>
       </c>
       <c r="P83">
-        <v>-54.46684678680003</v>
+        <v>-163.1646483376</v>
       </c>
       <c r="Q83">
-        <v>2.333153213199978</v>
+        <v>-106.3646483376</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3311932277514777</v>
+        <v>0.3668170683954349</v>
       </c>
       <c r="T83">
-        <v>4.152819204855806</v>
+        <v>4.671189492555045</v>
       </c>
       <c r="U83">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.2421645970219229</v>
+        <v>0.174881619270982</v>
       </c>
       <c r="W83">
-        <v>0.1112502371571817</v>
+        <v>0.1656837708503868</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.8072153234064099</v>
+        <v>0.5829387309032734</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2018877644084955</v>
+        <v>0.2034377644084954</v>
       </c>
       <c r="C84">
-        <v>-450.5975260910077</v>
+        <v>-492.4846737474454</v>
       </c>
       <c r="D84">
-        <v>807.9309339089924</v>
+        <v>799.9868162525547</v>
       </c>
       <c r="E84">
-        <v>2783.02546</v>
+        <v>2816.96849</v>
       </c>
       <c r="F84">
-        <v>2783.32846</v>
+        <v>2817.27149</v>
       </c>
       <c r="G84">
         <v>1524.8</v>
@@ -8303,37 +8303,37 @@
         <v>325.8</v>
       </c>
       <c r="M84">
-        <v>558.892354768</v>
+        <v>565.708115192</v>
       </c>
       <c r="N84">
-        <v>-233.092354768</v>
+        <v>-239.908115192</v>
       </c>
       <c r="O84">
-        <v>-69.92770643039999</v>
+        <v>-71.97243455760001</v>
       </c>
       <c r="P84">
-        <v>-163.1646483376</v>
+        <v>-167.9356806344</v>
       </c>
       <c r="Q84">
-        <v>-106.3646483376</v>
+        <v>-111.1356806344</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3668170683954349</v>
+        <v>0.3857004253598721</v>
       </c>
       <c r="T84">
-        <v>4.671189492555045</v>
+        <v>4.945965345058282</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.174881619270982</v>
+        <v>0.1727746118098859</v>
       </c>
       <c r="W84">
-        <v>0.1656837708503868</v>
+        <v>0.1661068579485749</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5829387309032734</v>
+        <v>0.5759153726996196</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2034377644084954</v>
+        <v>0.2049877644084954</v>
       </c>
       <c r="C85">
-        <v>-492.4846737474454</v>
+        <v>-534.2171187806857</v>
       </c>
       <c r="D85">
-        <v>799.9868162525547</v>
+        <v>792.1974012193142</v>
       </c>
       <c r="E85">
-        <v>2816.96849</v>
+        <v>2850.91152</v>
       </c>
       <c r="F85">
-        <v>2817.27149</v>
+        <v>2851.21452</v>
       </c>
       <c r="G85">
         <v>1524.8</v>
@@ -8385,37 +8385,37 @@
         <v>325.8</v>
       </c>
       <c r="M85">
-        <v>565.708115192</v>
+        <v>572.5238756160001</v>
       </c>
       <c r="N85">
-        <v>-239.908115192</v>
+        <v>-246.723875616</v>
       </c>
       <c r="O85">
-        <v>-71.97243455760001</v>
+        <v>-74.01716268480001</v>
       </c>
       <c r="P85">
-        <v>-167.9356806344</v>
+        <v>-172.7067129312</v>
       </c>
       <c r="Q85">
-        <v>-111.1356806344</v>
+        <v>-115.9067129312</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3857004253598721</v>
+        <v>0.4069442019448642</v>
       </c>
       <c r="T85">
-        <v>4.945965345058282</v>
+        <v>5.255088179124425</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1727746118098859</v>
+        <v>0.1707177711931015</v>
       </c>
       <c r="W85">
-        <v>0.1661068579485749</v>
+        <v>0.1665198715444252</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5759153726996196</v>
+        <v>0.5690592373103384</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2049877644084954</v>
+        <v>0.2065377644084954</v>
       </c>
       <c r="C86">
-        <v>-534.2171187806857</v>
+        <v>-575.7993365994821</v>
       </c>
       <c r="D86">
-        <v>792.1974012193142</v>
+        <v>784.558213400518</v>
       </c>
       <c r="E86">
-        <v>2850.91152</v>
+        <v>2884.85455</v>
       </c>
       <c r="F86">
-        <v>2851.21452</v>
+        <v>2885.15755</v>
       </c>
       <c r="G86">
         <v>1524.8</v>
@@ -8467,37 +8467,37 @@
         <v>325.8</v>
       </c>
       <c r="M86">
-        <v>572.5238756160001</v>
+        <v>579.33963604</v>
       </c>
       <c r="N86">
-        <v>-246.723875616</v>
+        <v>-253.5396360399999</v>
       </c>
       <c r="O86">
-        <v>-74.01716268480001</v>
+        <v>-76.06189081199999</v>
       </c>
       <c r="P86">
-        <v>-172.7067129312</v>
+        <v>-177.4777452279999</v>
       </c>
       <c r="Q86">
-        <v>-115.9067129312</v>
+        <v>-120.6777452279999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.406944201944864</v>
+        <v>0.4310204820745216</v>
       </c>
       <c r="T86">
-        <v>5.255088179124423</v>
+        <v>5.60542739106605</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1707177711931015</v>
+        <v>0.1687093268261239</v>
       </c>
       <c r="W86">
-        <v>0.1665198715444252</v>
+        <v>0.1669231671733143</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5690592373103384</v>
+        <v>0.5623644227537462</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2065377644084954</v>
+        <v>0.2080877644084954</v>
       </c>
       <c r="C87">
-        <v>-575.7993365994821</v>
+        <v>-617.2356316352229</v>
       </c>
       <c r="D87">
-        <v>784.558213400518</v>
+        <v>777.0649483647768</v>
       </c>
       <c r="E87">
-        <v>2884.85455</v>
+        <v>2918.79758</v>
       </c>
       <c r="F87">
-        <v>2885.15755</v>
+        <v>2919.10058</v>
       </c>
       <c r="G87">
         <v>1524.8</v>
@@ -8549,37 +8549,37 @@
         <v>325.8</v>
       </c>
       <c r="M87">
-        <v>579.33963604</v>
+        <v>586.155396464</v>
       </c>
       <c r="N87">
-        <v>-253.5396360399999</v>
+        <v>-260.355396464</v>
       </c>
       <c r="O87">
-        <v>-76.06189081199999</v>
+        <v>-78.10661893919999</v>
       </c>
       <c r="P87">
-        <v>-177.4777452279999</v>
+        <v>-182.2487775248</v>
       </c>
       <c r="Q87">
-        <v>-120.6777452279999</v>
+        <v>-125.4487775248</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4310204820745216</v>
+        <v>0.4585362307941303</v>
       </c>
       <c r="T87">
-        <v>5.60542739106605</v>
+        <v>6.005815061856483</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1687093268261239</v>
+        <v>0.1667475904676805</v>
       </c>
       <c r="W87">
-        <v>0.1669231671733143</v>
+        <v>0.1673170838340897</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5623644227537462</v>
+        <v>0.5558253015589352</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2080877644084954</v>
+        <v>0.2096377644084954</v>
       </c>
       <c r="C88">
-        <v>-617.2356316352229</v>
+        <v>-658.5301454296573</v>
       </c>
       <c r="D88">
-        <v>777.0649483647768</v>
+        <v>769.7134645703425</v>
       </c>
       <c r="E88">
-        <v>2918.79758</v>
+        <v>2952.74061</v>
       </c>
       <c r="F88">
-        <v>2919.10058</v>
+        <v>2953.04361</v>
       </c>
       <c r="G88">
         <v>1524.8</v>
@@ -8631,37 +8631,37 @@
         <v>325.8</v>
       </c>
       <c r="M88">
-        <v>586.155396464</v>
+        <v>592.971156888</v>
       </c>
       <c r="N88">
-        <v>-260.355396464</v>
+        <v>-267.171156888</v>
       </c>
       <c r="O88">
-        <v>-78.10661893919999</v>
+        <v>-80.15134706639999</v>
       </c>
       <c r="P88">
-        <v>-182.2487775248</v>
+        <v>-187.0198098216</v>
       </c>
       <c r="Q88">
-        <v>-125.4487775248</v>
+        <v>-130.2198098216</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4585362307941303</v>
+        <v>0.490285171624448</v>
       </c>
       <c r="T88">
-        <v>6.005815061856483</v>
+        <v>6.467800835845443</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1667475904676805</v>
+        <v>0.1648309514967877</v>
       </c>
       <c r="W88">
-        <v>0.1673170838340897</v>
+        <v>0.167701944939445</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5558253015589352</v>
+        <v>0.5494365049892922</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2096377644084954</v>
+        <v>0.2111877644084954</v>
       </c>
       <c r="C89">
-        <v>-658.5301454296573</v>
+        <v>-699.6868642678314</v>
       </c>
       <c r="D89">
-        <v>769.7134645703425</v>
+        <v>762.4997757321688</v>
       </c>
       <c r="E89">
-        <v>2952.74061</v>
+        <v>2986.68364</v>
       </c>
       <c r="F89">
-        <v>2953.04361</v>
+        <v>2986.98664</v>
       </c>
       <c r="G89">
         <v>1524.8</v>
@@ -8713,37 +8713,37 @@
         <v>325.8</v>
       </c>
       <c r="M89">
-        <v>592.971156888</v>
+        <v>599.786917312</v>
       </c>
       <c r="N89">
-        <v>-267.171156888</v>
+        <v>-273.986917312</v>
       </c>
       <c r="O89">
-        <v>-80.15134706639999</v>
+        <v>-82.1960751936</v>
       </c>
       <c r="P89">
-        <v>-187.0198098216</v>
+        <v>-191.7908421184</v>
       </c>
       <c r="Q89">
-        <v>-130.2198098216</v>
+        <v>-134.9908421184</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.490285171624448</v>
+        <v>0.5273256025931521</v>
       </c>
       <c r="T89">
-        <v>6.467800835845443</v>
+        <v>7.006784238832564</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1648309514967877</v>
+        <v>0.162957872502506</v>
       </c>
       <c r="W89">
-        <v>0.167701944939445</v>
+        <v>0.1680780592014968</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5494365049892922</v>
+        <v>0.5431929083416867</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2111877644084954</v>
+        <v>0.2127377644084955</v>
       </c>
       <c r="C90">
-        <v>-699.6868642678314</v>
+        <v>-740.7096263858007</v>
       </c>
       <c r="D90">
-        <v>762.4997757321688</v>
+        <v>755.4200436141991</v>
       </c>
       <c r="E90">
-        <v>2986.68364</v>
+        <v>3020.62667</v>
       </c>
       <c r="F90">
-        <v>2986.98664</v>
+        <v>3020.92967</v>
       </c>
       <c r="G90">
         <v>1524.8</v>
@@ -8795,37 +8795,37 @@
         <v>325.8</v>
       </c>
       <c r="M90">
-        <v>599.786917312</v>
+        <v>606.602677736</v>
       </c>
       <c r="N90">
-        <v>-273.986917312</v>
+        <v>-280.802677736</v>
       </c>
       <c r="O90">
-        <v>-82.1960751936</v>
+        <v>-84.2408033208</v>
       </c>
       <c r="P90">
-        <v>-191.7908421184</v>
+        <v>-196.5618744152</v>
       </c>
       <c r="Q90">
-        <v>-134.9908421184</v>
+        <v>-139.7618744152</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5273256025931521</v>
+        <v>0.5711006573743477</v>
       </c>
       <c r="T90">
-        <v>7.006784238832564</v>
+        <v>7.643764624180979</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.162957872502506</v>
+        <v>0.1611268851710172</v>
       </c>
       <c r="W90">
-        <v>0.1680780592014968</v>
+        <v>0.1684457214576598</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5431929083416867</v>
+        <v>0.5370896172367239</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2127377644084955</v>
+        <v>0.2142877644084954</v>
       </c>
       <c r="C91">
-        <v>-740.7096263858007</v>
+        <v>-781.6021287805033</v>
       </c>
       <c r="D91">
-        <v>755.4200436141991</v>
+        <v>748.4705712194966</v>
       </c>
       <c r="E91">
-        <v>3020.62667</v>
+        <v>3054.5697</v>
       </c>
       <c r="F91">
-        <v>3020.92967</v>
+        <v>3054.8727</v>
       </c>
       <c r="G91">
         <v>1524.8</v>
@@ -8877,37 +8877,37 @@
         <v>325.8</v>
       </c>
       <c r="M91">
-        <v>606.602677736</v>
+        <v>613.4184381600001</v>
       </c>
       <c r="N91">
-        <v>-280.802677736</v>
+        <v>-287.61843816</v>
       </c>
       <c r="O91">
-        <v>-84.2408033208</v>
+        <v>-86.28553144800001</v>
       </c>
       <c r="P91">
-        <v>-196.5618744152</v>
+        <v>-201.332906712</v>
       </c>
       <c r="Q91">
-        <v>-139.7618744152</v>
+        <v>-144.532906712</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5711006573743477</v>
+        <v>0.6236307231117825</v>
       </c>
       <c r="T91">
-        <v>7.643764624180979</v>
+        <v>8.408141086599077</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1611268851710172</v>
+        <v>0.1593365864468947</v>
       </c>
       <c r="W91">
-        <v>0.1684457214576598</v>
+        <v>0.1688052134414635</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5370896172367239</v>
+        <v>0.5311219548229824</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2142877644084954</v>
+        <v>0.2158377644084954</v>
       </c>
       <c r="C92">
-        <v>-781.6021287805033</v>
+        <v>-822.3679336471687</v>
       </c>
       <c r="D92">
-        <v>748.4705712194966</v>
+        <v>741.6477963528312</v>
       </c>
       <c r="E92">
-        <v>3054.5697</v>
+        <v>3088.51273</v>
       </c>
       <c r="F92">
-        <v>3054.8727</v>
+        <v>3088.81573</v>
       </c>
       <c r="G92">
         <v>1524.8</v>
@@ -8959,37 +8959,37 @@
         <v>325.8</v>
       </c>
       <c r="M92">
-        <v>613.4184381600001</v>
+        <v>620.234198584</v>
       </c>
       <c r="N92">
-        <v>-287.61843816</v>
+        <v>-294.4341985839999</v>
       </c>
       <c r="O92">
-        <v>-86.28553144800001</v>
+        <v>-88.33025957519997</v>
       </c>
       <c r="P92">
-        <v>-201.332906712</v>
+        <v>-206.1039390088</v>
       </c>
       <c r="Q92">
-        <v>-144.532906712</v>
+        <v>-149.3039390087999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6236307231117825</v>
+        <v>0.6878341367908696</v>
       </c>
       <c r="T92">
-        <v>8.408141086599077</v>
+        <v>9.342378985110088</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1593365864468947</v>
+        <v>0.1575856349474783</v>
       </c>
       <c r="W92">
-        <v>0.1688052134414635</v>
+        <v>0.1691568045025464</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5311219548229824</v>
+        <v>0.5252854498249278</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2158377644084954</v>
+        <v>0.2173877644084954</v>
       </c>
       <c r="C93">
-        <v>-822.3679336471687</v>
+        <v>-863.0104744678251</v>
       </c>
       <c r="D93">
-        <v>741.6477963528312</v>
+        <v>734.9482855321752</v>
       </c>
       <c r="E93">
-        <v>3088.51273</v>
+        <v>3122.45576</v>
       </c>
       <c r="F93">
-        <v>3088.81573</v>
+        <v>3122.75876</v>
       </c>
       <c r="G93">
         <v>1524.8</v>
@@ -9041,37 +9041,37 @@
         <v>325.8</v>
       </c>
       <c r="M93">
-        <v>620.234198584</v>
+        <v>627.0499590080001</v>
       </c>
       <c r="N93">
-        <v>-294.4341985839999</v>
+        <v>-301.2499590080001</v>
       </c>
       <c r="O93">
-        <v>-88.33025957519997</v>
+        <v>-90.37498770240002</v>
       </c>
       <c r="P93">
-        <v>-206.1039390088</v>
+        <v>-210.8749713056001</v>
       </c>
       <c r="Q93">
-        <v>-149.3039390087999</v>
+        <v>-154.0749713056001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6878341367908696</v>
+        <v>0.7680884038897284</v>
       </c>
       <c r="T93">
-        <v>9.342378985110088</v>
+        <v>10.51017635824885</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1575856349474783</v>
+        <v>0.1558727476110927</v>
       </c>
       <c r="W93">
-        <v>0.1691568045025464</v>
+        <v>0.1695007522796926</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5252854498249278</v>
+        <v>0.5195758253703089</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2173877644084954</v>
+        <v>0.2189377644084954</v>
       </c>
       <c r="C94">
-        <v>-863.0104744678251</v>
+        <v>-903.5330617727645</v>
       </c>
       <c r="D94">
-        <v>734.9482855321752</v>
+        <v>728.3687282272355</v>
       </c>
       <c r="E94">
-        <v>3122.45576</v>
+        <v>3156.39879</v>
       </c>
       <c r="F94">
-        <v>3122.75876</v>
+        <v>3156.70179</v>
       </c>
       <c r="G94">
         <v>1524.8</v>
@@ -9123,37 +9123,37 @@
         <v>325.8</v>
       </c>
       <c r="M94">
-        <v>627.0499590080001</v>
+        <v>633.865719432</v>
       </c>
       <c r="N94">
-        <v>-301.2499590080001</v>
+        <v>-308.065719432</v>
       </c>
       <c r="O94">
-        <v>-90.37498770240002</v>
+        <v>-92.41971582959999</v>
       </c>
       <c r="P94">
-        <v>-210.8749713056001</v>
+        <v>-215.6460036024</v>
       </c>
       <c r="Q94">
-        <v>-154.0749713056001</v>
+        <v>-158.8460036024</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7680884038897284</v>
+        <v>0.8712724615882611</v>
       </c>
       <c r="T94">
-        <v>10.51017635824885</v>
+        <v>12.01163012371297</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1558727476110927</v>
+        <v>0.1541966965615111</v>
       </c>
       <c r="W94">
-        <v>0.1695007522796926</v>
+        <v>0.1698373033304486</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5195758253703089</v>
+        <v>0.5139889885383702</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2189377644084954</v>
+        <v>0.2204877644084955</v>
       </c>
       <c r="C95">
-        <v>-903.5330617727645</v>
+        <v>-943.938888595284</v>
       </c>
       <c r="D95">
-        <v>728.3687282272355</v>
+        <v>721.9059314047162</v>
       </c>
       <c r="E95">
-        <v>3156.39879</v>
+        <v>3190.34182</v>
       </c>
       <c r="F95">
-        <v>3156.70179</v>
+        <v>3190.64482</v>
       </c>
       <c r="G95">
         <v>1524.8</v>
@@ -9205,37 +9205,37 @@
         <v>325.8</v>
       </c>
       <c r="M95">
-        <v>633.865719432</v>
+        <v>640.681479856</v>
       </c>
       <c r="N95">
-        <v>-308.065719432</v>
+        <v>-314.881479856</v>
       </c>
       <c r="O95">
-        <v>-92.41971582959999</v>
+        <v>-94.4644439568</v>
       </c>
       <c r="P95">
-        <v>-215.6460036024</v>
+        <v>-220.4170358992</v>
       </c>
       <c r="Q95">
-        <v>-158.8460036024</v>
+        <v>-163.6170358992</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8712724615882611</v>
+        <v>1.008851205186305</v>
       </c>
       <c r="T95">
-        <v>12.01163012371297</v>
+        <v>14.01356847766514</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1541966965615111</v>
+        <v>0.1525563061725588</v>
       </c>
       <c r="W95">
-        <v>0.1698373033304486</v>
+        <v>0.1701666937205502</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5139889885383702</v>
+        <v>0.508521020575196</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2204877644084955</v>
+        <v>0.2220377644084954</v>
       </c>
       <c r="C96">
-        <v>-943.938888595284</v>
+        <v>-984.2310356385738</v>
       </c>
       <c r="D96">
-        <v>721.9059314047162</v>
+        <v>715.5568143614262</v>
       </c>
       <c r="E96">
-        <v>3190.34182</v>
+        <v>3224.28485</v>
       </c>
       <c r="F96">
-        <v>3190.64482</v>
+        <v>3224.58785</v>
       </c>
       <c r="G96">
         <v>1524.8</v>
@@ -9287,37 +9287,37 @@
         <v>325.8</v>
       </c>
       <c r="M96">
-        <v>640.681479856</v>
+        <v>647.49724028</v>
       </c>
       <c r="N96">
-        <v>-314.881479856</v>
+        <v>-321.69724028</v>
       </c>
       <c r="O96">
-        <v>-94.4644439568</v>
+        <v>-96.509172084</v>
       </c>
       <c r="P96">
-        <v>-220.4170358992</v>
+        <v>-225.188068196</v>
       </c>
       <c r="Q96">
-        <v>-163.6170358992</v>
+        <v>-168.388068196</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.008851205186305</v>
+        <v>1.201461446223566</v>
       </c>
       <c r="T96">
-        <v>14.01356847766514</v>
+        <v>16.81628217319818</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1525563061725588</v>
+        <v>0.1509504503181108</v>
       </c>
       <c r="W96">
-        <v>0.1701666937205502</v>
+        <v>0.1704891495761233</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.508521020575196</v>
+        <v>0.5031681677270361</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2220377644084954</v>
+        <v>0.2586236052606996</v>
       </c>
       <c r="C97">
-        <v>-984.2310356385738</v>
+        <v>-1141.183201297511</v>
       </c>
       <c r="D97">
-        <v>715.5568143614262</v>
+        <v>592.5476787024899</v>
       </c>
       <c r="E97">
-        <v>3224.28485</v>
+        <v>3258.22788</v>
       </c>
       <c r="F97">
-        <v>3224.58785</v>
+        <v>3258.53088</v>
       </c>
       <c r="G97">
         <v>1524.8</v>
@@ -9369,45 +9369,45 @@
         <v>325.8</v>
       </c>
       <c r="M97">
-        <v>647.49724028</v>
+        <v>768.3615815040001</v>
       </c>
       <c r="N97">
-        <v>-321.69724028</v>
+        <v>-442.5615815040001</v>
       </c>
       <c r="O97">
-        <v>-96.509172084</v>
+        <v>-132.7684744512</v>
       </c>
       <c r="P97">
-        <v>-225.188068196</v>
+        <v>-309.7931070528001</v>
       </c>
       <c r="Q97">
-        <v>-168.388068196</v>
+        <v>-252.9931070528001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.201461446223566</v>
+        <v>1.526272829084563</v>
       </c>
       <c r="T97">
-        <v>16.81628217319818</v>
+        <v>21.54268356445871</v>
       </c>
       <c r="U97">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1509504503181108</v>
+        <v>0.127205735363138</v>
       </c>
       <c r="W97">
-        <v>0.1704891495761233</v>
+        <v>0.2058048876013721</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.5031681677270361</v>
+        <v>0.4240191178771265</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2586236052606997</v>
+        <v>0.2605236052606996</v>
       </c>
       <c r="C98">
-        <v>-1141.18320129751</v>
+        <v>-1180.369439598562</v>
       </c>
       <c r="D98">
-        <v>592.5476787024896</v>
+        <v>587.3044704014377</v>
       </c>
       <c r="E98">
-        <v>3258.22788</v>
+        <v>3292.17091</v>
       </c>
       <c r="F98">
-        <v>3258.53088</v>
+        <v>3292.47391</v>
       </c>
       <c r="G98">
         <v>1524.8</v>
@@ -9451,37 +9451,37 @@
         <v>325.8</v>
       </c>
       <c r="M98">
-        <v>768.361581504</v>
+        <v>776.3653479779999</v>
       </c>
       <c r="N98">
-        <v>-442.561581504</v>
+        <v>-450.5653479779999</v>
       </c>
       <c r="O98">
-        <v>-132.7684744512</v>
+        <v>-135.1696043934</v>
       </c>
       <c r="P98">
-        <v>-309.7931070528</v>
+        <v>-315.3957435845999</v>
       </c>
       <c r="Q98">
-        <v>-252.9931070528</v>
+        <v>-258.5957435845999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.52627282908456</v>
+        <v>2.019763772112745</v>
       </c>
       <c r="T98">
-        <v>21.54268356445866</v>
+        <v>28.72357808594487</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.127205735363138</v>
+        <v>0.1258943360294974</v>
       </c>
       <c r="W98">
-        <v>0.2058048876013721</v>
+        <v>0.2061141155642445</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4240191178771267</v>
+        <v>0.4196477867649914</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2605236052606996</v>
+        <v>0.2624236052606996</v>
       </c>
       <c r="C99">
-        <v>-1180.369439598562</v>
+        <v>-1219.463701812705</v>
       </c>
       <c r="D99">
-        <v>587.3044704014377</v>
+        <v>582.1532381872948</v>
       </c>
       <c r="E99">
-        <v>3292.17091</v>
+        <v>3326.11394</v>
       </c>
       <c r="F99">
-        <v>3292.47391</v>
+        <v>3326.41694</v>
       </c>
       <c r="G99">
         <v>1524.8</v>
@@ -9533,37 +9533,37 @@
         <v>325.8</v>
       </c>
       <c r="M99">
-        <v>776.3653479779999</v>
+        <v>784.369114452</v>
       </c>
       <c r="N99">
-        <v>-450.5653479779999</v>
+        <v>-458.569114452</v>
       </c>
       <c r="O99">
-        <v>-135.1696043934</v>
+        <v>-137.5707343356</v>
       </c>
       <c r="P99">
-        <v>-315.3957435845999</v>
+        <v>-320.9983801164</v>
       </c>
       <c r="Q99">
-        <v>-258.5957435845999</v>
+        <v>-264.1983801164</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.019763772112745</v>
+        <v>3.006745658169118</v>
       </c>
       <c r="T99">
-        <v>28.72357808594487</v>
+        <v>43.08536712891731</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1258943360294974</v>
+        <v>0.1246096999475637</v>
       </c>
       <c r="W99">
-        <v>0.2061141155642445</v>
+        <v>0.2064170327523645</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4196477867649914</v>
+        <v>0.4153656664918791</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2624236052606996</v>
+        <v>0.2643236052606996</v>
       </c>
       <c r="C100">
-        <v>-1219.463701812705</v>
+        <v>-1258.468387056935</v>
       </c>
       <c r="D100">
-        <v>582.1532381872948</v>
+        <v>577.0915829430647</v>
       </c>
       <c r="E100">
-        <v>3326.11394</v>
+        <v>3360.05697</v>
       </c>
       <c r="F100">
-        <v>3326.41694</v>
+        <v>3360.35997</v>
       </c>
       <c r="G100">
         <v>1524.8</v>
@@ -9615,37 +9615,37 @@
         <v>325.8</v>
       </c>
       <c r="M100">
-        <v>784.369114452</v>
+        <v>792.372880926</v>
       </c>
       <c r="N100">
-        <v>-458.569114452</v>
+        <v>-466.572880926</v>
       </c>
       <c r="O100">
-        <v>-137.5707343356</v>
+        <v>-139.9718642778</v>
       </c>
       <c r="P100">
-        <v>-320.9983801164</v>
+        <v>-326.6010166482</v>
       </c>
       <c r="Q100">
-        <v>-264.1983801164</v>
+        <v>-269.8010166482</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.006745658169118</v>
+        <v>5.967691316338238</v>
       </c>
       <c r="T100">
-        <v>43.08536712891731</v>
+        <v>86.17073425783462</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1246096999475637</v>
+        <v>0.1233510161097096</v>
       </c>
       <c r="W100">
-        <v>0.2064170327523645</v>
+        <v>0.2067138304013305</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4153656664918791</v>
+        <v>0.4111700536990319</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2643236052606996</v>
-      </c>
-      <c r="C101">
-        <v>-1258.468387056935</v>
-      </c>
-      <c r="D101">
-        <v>577.0915829430647</v>
-      </c>
-      <c r="E101">
-        <v>3360.05697</v>
-      </c>
-      <c r="F101">
-        <v>3360.35997</v>
-      </c>
-      <c r="G101">
-        <v>1524.8</v>
-      </c>
-      <c r="H101">
-        <v>3394</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>382.6</v>
-      </c>
-      <c r="K101">
-        <v>56.80000000000001</v>
-      </c>
-      <c r="L101">
-        <v>325.8</v>
-      </c>
-      <c r="M101">
-        <v>792.372880926</v>
-      </c>
-      <c r="N101">
-        <v>-466.572880926</v>
-      </c>
-      <c r="O101">
-        <v>-139.9718642778</v>
-      </c>
-      <c r="P101">
-        <v>-326.6010166482</v>
-      </c>
-      <c r="Q101">
-        <v>-269.8010166482</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.967691316338238</v>
-      </c>
-      <c r="T101">
-        <v>86.17073425783462</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1233510161097096</v>
-      </c>
-      <c r="W101">
-        <v>0.2067138304013305</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4111700536990319</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
